--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283205</v>
+        <v>125283515</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>92326</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589702</v>
+        <v>589701</v>
       </c>
       <c r="R2" t="n">
-        <v>6931407</v>
+        <v>6931425</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +789,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125284804</v>
+        <v>125283192</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -823,7 +837,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589522</v>
+        <v>589701</v>
       </c>
       <c r="R3" t="n">
-        <v>6931472</v>
+        <v>6931425</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +911,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125285335</v>
+        <v>125285548</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,27 +939,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +968,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589527</v>
+        <v>589543</v>
       </c>
       <c r="R4" t="n">
-        <v>6931442</v>
+        <v>6931382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1040,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125285099</v>
+        <v>125283173</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1071,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589466</v>
+        <v>589711</v>
       </c>
       <c r="R5" t="n">
-        <v>6931475</v>
+        <v>6931414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,24 +1118,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1140,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125283801</v>
+        <v>125284424</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,16 +1168,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1193,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589633</v>
+        <v>589508</v>
       </c>
       <c r="R6" t="n">
-        <v>6931451</v>
+        <v>6931482</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125283515</v>
+        <v>125287385</v>
       </c>
       <c r="B7" t="n">
-        <v>92326</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,47 +1281,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589701</v>
+        <v>589447</v>
       </c>
       <c r="R7" t="n">
-        <v>6931425</v>
+        <v>6931328</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1364,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,19 +1369,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125285776</v>
+        <v>125283973</v>
       </c>
       <c r="B8" t="n">
         <v>91023</v>
@@ -1436,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589446</v>
+        <v>589587</v>
       </c>
       <c r="R8" t="n">
-        <v>6931392</v>
+        <v>6931481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125284988</v>
+        <v>125283205</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,42 +1505,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589474</v>
+        <v>589702</v>
       </c>
       <c r="R9" t="n">
-        <v>6931483</v>
+        <v>6931407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,22 +1593,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125285242</v>
+        <v>125286793</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,16 +1621,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1669,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589459</v>
+        <v>589614</v>
       </c>
       <c r="R10" t="n">
-        <v>6931441</v>
+        <v>6931331</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1704,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,19 +1715,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125283329</v>
+        <v>125285519</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1786,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589665</v>
+        <v>589515</v>
       </c>
       <c r="R11" t="n">
-        <v>6931444</v>
+        <v>6931442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1821,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1831,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1863,10 +1849,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125283192</v>
+        <v>125283329</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,31 +1861,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1908,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589701</v>
+        <v>589665</v>
       </c>
       <c r="R12" t="n">
-        <v>6931425</v>
+        <v>6931444</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,12 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,22 +1959,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125286606</v>
+        <v>125283936</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1997,31 +1983,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2030,10 +2016,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589602</v>
+        <v>589597</v>
       </c>
       <c r="R13" t="n">
-        <v>6931356</v>
+        <v>6931482</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,7 +2051,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2075,7 +2061,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,7 +2093,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125291148</v>
+        <v>125284981</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2147,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589727</v>
+        <v>589475</v>
       </c>
       <c r="R14" t="n">
-        <v>6931355</v>
+        <v>6931470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,7 +2173,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2192,12 +2183,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2212,19 +2203,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125286321</v>
+        <v>125283860</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2269,10 +2260,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589560</v>
+        <v>589606</v>
       </c>
       <c r="R15" t="n">
-        <v>6931398</v>
+        <v>6931471</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,7 +2305,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2346,10 +2337,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125284936</v>
+        <v>125285099</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,30 +2349,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2390,10 +2382,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589486</v>
+        <v>589466</v>
       </c>
       <c r="R16" t="n">
-        <v>6931494</v>
+        <v>6931475</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2425,7 +2417,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2435,7 +2427,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,10 +2459,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125284607</v>
+        <v>125285600</v>
       </c>
       <c r="B17" t="n">
-        <v>92326</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,47 +2471,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589522</v>
+        <v>589438</v>
       </c>
       <c r="R17" t="n">
-        <v>6931472</v>
+        <v>6931387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2546,7 +2534,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2556,12 +2544,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,22 +2559,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125285548</v>
+        <v>125286102</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2604,27 +2587,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2633,10 +2616,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589543</v>
+        <v>589438</v>
       </c>
       <c r="R18" t="n">
-        <v>6931382</v>
+        <v>6931387</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,7 +2651,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,7 +2661,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2693,22 +2681,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125283173</v>
+        <v>125286606</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,16 +2709,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2750,10 +2738,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589711</v>
+        <v>589602</v>
       </c>
       <c r="R19" t="n">
-        <v>6931414</v>
+        <v>6931356</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2783,14 +2771,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2939,10 +2932,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125284367</v>
+        <v>125285776</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>91023</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2951,25 +2944,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2979,10 +2972,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589508</v>
+        <v>589446</v>
       </c>
       <c r="R21" t="n">
-        <v>6931482</v>
+        <v>6931392</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3014,7 +3007,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3024,12 +3017,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Enormt mycket lunglav</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3044,22 +3032,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125284881</v>
+        <v>125285367</v>
       </c>
       <c r="B22" t="n">
-        <v>91012</v>
+        <v>105117</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,25 +3056,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3096,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589483</v>
+        <v>589527</v>
       </c>
       <c r="R22" t="n">
-        <v>6931476</v>
+        <v>6931442</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3131,7 +3119,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3141,7 +3129,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3168,10 +3156,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125287385</v>
+        <v>125285335</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3184,16 +3172,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3202,16 +3190,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589447</v>
+        <v>589527</v>
       </c>
       <c r="R23" t="n">
-        <v>6931328</v>
+        <v>6931442</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3243,7 +3236,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3253,7 +3246,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3280,10 +3278,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125290551</v>
+        <v>125286059</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,34 +3294,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589606</v>
+        <v>589552</v>
       </c>
       <c r="R24" t="n">
-        <v>6931325</v>
+        <v>6931425</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3355,7 +3358,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3365,7 +3368,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3380,22 +3388,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125287027</v>
+        <v>125286223</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3404,38 +3412,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589571</v>
+        <v>589552</v>
       </c>
       <c r="R25" t="n">
-        <v>6931323</v>
+        <v>6931425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3467,7 +3480,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3477,7 +3490,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3504,10 +3517,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125286793</v>
+        <v>125285293</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3520,16 +3533,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3549,10 +3562,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589614</v>
+        <v>589459</v>
       </c>
       <c r="R26" t="n">
-        <v>6931331</v>
+        <v>6931441</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3584,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3594,12 +3607,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3614,22 +3627,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125286223</v>
+        <v>125290527</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3642,16 +3655,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3671,10 +3684,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589552</v>
+        <v>589624</v>
       </c>
       <c r="R27" t="n">
-        <v>6931425</v>
+        <v>6931325</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3706,7 +3719,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3716,7 +3729,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3731,22 +3749,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283936</v>
+        <v>125283250</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>57995</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3755,31 +3773,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>103018</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3788,10 +3806,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589597</v>
+        <v>589679</v>
       </c>
       <c r="R28" t="n">
-        <v>6931482</v>
+        <v>6931418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3823,7 +3841,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3833,12 +3851,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3865,10 +3878,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125284312</v>
+        <v>125283609</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3881,39 +3894,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589522</v>
+        <v>589655</v>
       </c>
       <c r="R29" t="n">
-        <v>6931472</v>
+        <v>6931459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3945,7 +3953,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3955,12 +3963,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3987,7 +3990,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125284981</v>
+        <v>125286321</v>
       </c>
       <c r="B30" t="n">
         <v>57513</v>
@@ -4032,10 +4035,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589475</v>
+        <v>589560</v>
       </c>
       <c r="R30" t="n">
-        <v>6931470</v>
+        <v>6931398</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4067,7 +4070,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4077,12 +4080,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4109,10 +4112,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125285600</v>
+        <v>125284804</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4121,38 +4124,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589438</v>
+        <v>589522</v>
       </c>
       <c r="R31" t="n">
-        <v>6931387</v>
+        <v>6931472</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4184,7 +4192,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4194,7 +4202,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4209,22 +4217,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125286059</v>
+        <v>125284251</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4237,27 +4245,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4266,10 +4273,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589552</v>
+        <v>589508</v>
       </c>
       <c r="R32" t="n">
-        <v>6931425</v>
+        <v>6931482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4308,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,12 +4318,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,22 +4333,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125285293</v>
+        <v>125290551</v>
       </c>
       <c r="B33" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4359,39 +4361,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589459</v>
+        <v>589606</v>
       </c>
       <c r="R33" t="n">
-        <v>6931441</v>
+        <v>6931325</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4423,7 +4420,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4433,12 +4430,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Fjäder Järpe</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4465,10 +4457,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125283250</v>
+        <v>125285242</v>
       </c>
       <c r="B34" t="n">
-        <v>57995</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4481,27 +4473,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4510,10 +4502,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589679</v>
+        <v>589459</v>
       </c>
       <c r="R34" t="n">
-        <v>6931418</v>
+        <v>6931441</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4555,7 +4547,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4570,22 +4562,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125285367</v>
+        <v>125283801</v>
       </c>
       <c r="B35" t="n">
-        <v>105117</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4594,38 +4586,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589527</v>
+        <v>589633</v>
       </c>
       <c r="R35" t="n">
-        <v>6931442</v>
+        <v>6931451</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4657,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4667,7 +4664,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4682,22 +4684,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125285519</v>
+        <v>125284988</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4710,27 +4712,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4739,10 +4740,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589515</v>
+        <v>589474</v>
       </c>
       <c r="R36" t="n">
-        <v>6931442</v>
+        <v>6931483</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4774,7 +4775,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4784,12 +4785,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4804,19 +4800,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125283860</v>
+        <v>125284312</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4861,10 +4857,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589606</v>
+        <v>589522</v>
       </c>
       <c r="R37" t="n">
-        <v>6931471</v>
+        <v>6931472</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4896,7 +4892,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4906,7 +4902,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4938,10 +4934,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125284424</v>
+        <v>125283953</v>
       </c>
       <c r="B38" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4954,27 +4950,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4983,10 +4978,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589508</v>
+        <v>589633</v>
       </c>
       <c r="R38" t="n">
-        <v>6931482</v>
+        <v>6931451</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5018,7 +5013,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5028,7 +5023,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5055,10 +5050,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125283973</v>
+        <v>125284367</v>
       </c>
       <c r="B39" t="n">
-        <v>91023</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5067,25 +5062,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5095,10 +5090,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589587</v>
+        <v>589508</v>
       </c>
       <c r="R39" t="n">
-        <v>6931481</v>
+        <v>6931482</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5130,7 +5125,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5140,7 +5135,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5155,22 +5155,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125283953</v>
+        <v>125284881</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5183,38 +5183,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589633</v>
+        <v>589483</v>
       </c>
       <c r="R40" t="n">
-        <v>6931451</v>
+        <v>6931476</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5246,7 +5242,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5256,7 +5252,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5271,22 +5267,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125286102</v>
+        <v>125287027</v>
       </c>
       <c r="B41" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5295,43 +5291,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589438</v>
+        <v>589571</v>
       </c>
       <c r="R41" t="n">
-        <v>6931387</v>
+        <v>6931323</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5363,7 +5354,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5373,12 +5364,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5393,22 +5379,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125290527</v>
+        <v>125284607</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>92326</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5417,31 +5403,35 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5450,10 +5440,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589624</v>
+        <v>589522</v>
       </c>
       <c r="R42" t="n">
-        <v>6931325</v>
+        <v>6931472</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5485,7 +5475,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5495,12 +5485,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5515,22 +5505,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125283609</v>
+        <v>125284936</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5539,38 +5529,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589655</v>
+        <v>589486</v>
       </c>
       <c r="R43" t="n">
-        <v>6931459</v>
+        <v>6931494</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5602,7 +5596,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5612,7 +5606,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5627,22 +5621,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125284251</v>
+        <v>125291148</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5655,26 +5649,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5683,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589508</v>
+        <v>589727</v>
       </c>
       <c r="R44" t="n">
-        <v>6931482</v>
+        <v>6931355</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5718,7 +5713,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5728,7 +5723,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5752,6 +5752,596 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125316461</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>589678</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6931231</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125316757</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>589713</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6931246</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125316811</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>589717</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6931206</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125316951</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>589777</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6931248</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125316739</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>589717</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6931235</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-22</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283515</v>
+        <v>125283953</v>
       </c>
       <c r="B2" t="n">
-        <v>92326</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589701</v>
+        <v>589633</v>
       </c>
       <c r="R2" t="n">
-        <v>6931425</v>
+        <v>6931451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125283192</v>
+        <v>125285242</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,31 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589701</v>
+        <v>589459</v>
       </c>
       <c r="R3" t="n">
-        <v>6931425</v>
+        <v>6931441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125285548</v>
+        <v>125285335</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,27 +924,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -968,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589543</v>
+        <v>589527</v>
       </c>
       <c r="R4" t="n">
-        <v>6931382</v>
+        <v>6931442</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125283173</v>
+        <v>125285367</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,43 +1042,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589711</v>
+        <v>589527</v>
       </c>
       <c r="R5" t="n">
-        <v>6931414</v>
+        <v>6931442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,14 +1103,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125284424</v>
+        <v>125283173</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,16 +1158,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1197,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589508</v>
+        <v>589711</v>
       </c>
       <c r="R6" t="n">
-        <v>6931482</v>
+        <v>6931414</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,19 +1220,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:53</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125287385</v>
+        <v>125284881</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,21 +1270,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589447</v>
+        <v>589483</v>
       </c>
       <c r="R7" t="n">
-        <v>6931328</v>
+        <v>6931476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125283973</v>
+        <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,38 +1378,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589587</v>
+        <v>589552</v>
       </c>
       <c r="R8" t="n">
-        <v>6931481</v>
+        <v>6931425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125283205</v>
+        <v>125285600</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,25 +1495,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,10 +1523,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589702</v>
+        <v>589438</v>
       </c>
       <c r="R9" t="n">
-        <v>6931407</v>
+        <v>6931387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1558,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1568,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,19 +1583,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125286793</v>
+        <v>125291148</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1650,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589614</v>
+        <v>589727</v>
       </c>
       <c r="R10" t="n">
-        <v>6931331</v>
+        <v>6931355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,12 +1685,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,19 +1705,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125285519</v>
+        <v>125283860</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1772,10 +1762,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589515</v>
+        <v>589606</v>
       </c>
       <c r="R11" t="n">
-        <v>6931442</v>
+        <v>6931471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1849,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125283329</v>
+        <v>125284607</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>92326</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,31 +1851,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1894,10 +1888,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589665</v>
+        <v>589522</v>
       </c>
       <c r="R12" t="n">
-        <v>6931444</v>
+        <v>6931472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1923,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1933,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125283936</v>
+        <v>125286606</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,31 +1977,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2016,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589597</v>
+        <v>589602</v>
       </c>
       <c r="R13" t="n">
-        <v>6931482</v>
+        <v>6931356</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2051,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2061,12 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,7 +2082,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125284981</v>
+        <v>125286793</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2138,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589475</v>
+        <v>589614</v>
       </c>
       <c r="R14" t="n">
-        <v>6931470</v>
+        <v>6931331</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2173,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2183,12 +2172,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,7 +2204,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125283860</v>
+        <v>125284312</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2260,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589606</v>
+        <v>589522</v>
       </c>
       <c r="R15" t="n">
-        <v>6931471</v>
+        <v>6931472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,7 +2294,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2337,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125285099</v>
+        <v>125283515</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>92326</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2349,31 +2338,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2382,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589466</v>
+        <v>589701</v>
       </c>
       <c r="R16" t="n">
-        <v>6931475</v>
+        <v>6931425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2417,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2427,12 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2459,10 +2452,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125285600</v>
+        <v>125285293</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2475,34 +2468,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589438</v>
+        <v>589459</v>
       </c>
       <c r="R17" t="n">
-        <v>6931387</v>
+        <v>6931441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2534,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2544,7 +2542,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2571,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125286102</v>
+        <v>125283973</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91023</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2583,43 +2586,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589438</v>
+        <v>589587</v>
       </c>
       <c r="R18" t="n">
-        <v>6931387</v>
+        <v>6931481</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2651,7 +2649,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2661,12 +2659,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2681,22 +2674,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125286606</v>
+        <v>125284251</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2709,27 +2702,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2738,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589602</v>
+        <v>589508</v>
       </c>
       <c r="R19" t="n">
-        <v>6931356</v>
+        <v>6931482</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2773,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2783,7 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2798,22 +2790,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125284432</v>
+        <v>125283250</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57995</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2826,27 +2818,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2855,10 +2847,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589518</v>
+        <v>589679</v>
       </c>
       <c r="R20" t="n">
-        <v>6931461</v>
+        <v>6931418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2890,7 +2882,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2900,12 +2892,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2932,10 +2919,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125285776</v>
+        <v>125285548</v>
       </c>
       <c r="B21" t="n">
-        <v>91023</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2944,38 +2931,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589446</v>
+        <v>589543</v>
       </c>
       <c r="R21" t="n">
-        <v>6931392</v>
+        <v>6931382</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3007,7 +2999,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3017,7 +3009,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3044,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125285367</v>
+        <v>125283205</v>
       </c>
       <c r="B22" t="n">
-        <v>105117</v>
+        <v>96979</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3060,21 +3052,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3084,10 +3076,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589527</v>
+        <v>589702</v>
       </c>
       <c r="R22" t="n">
-        <v>6931442</v>
+        <v>6931407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3119,7 +3111,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3129,7 +3121,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3156,7 +3148,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125285335</v>
+        <v>125286321</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3201,10 +3193,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589527</v>
+        <v>589560</v>
       </c>
       <c r="R23" t="n">
-        <v>6931442</v>
+        <v>6931398</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3236,7 +3228,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3246,12 +3238,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3278,7 +3270,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125286059</v>
+        <v>125285519</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3323,10 +3315,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589552</v>
+        <v>589515</v>
       </c>
       <c r="R24" t="n">
-        <v>6931425</v>
+        <v>6931442</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3358,7 +3350,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3368,7 +3360,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3400,10 +3392,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125286223</v>
+        <v>125286059</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3416,16 +3408,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3480,7 +3472,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3490,7 +3482,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3517,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125285293</v>
+        <v>125284981</v>
       </c>
       <c r="B26" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3533,16 +3530,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3562,10 +3559,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589459</v>
+        <v>589475</v>
       </c>
       <c r="R26" t="n">
-        <v>6931441</v>
+        <v>6931470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3594,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,12 +3604,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fjäder Järpe</t>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3627,22 +3624,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125290527</v>
+        <v>125284424</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3655,16 +3652,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3684,10 +3681,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589624</v>
+        <v>589508</v>
       </c>
       <c r="R27" t="n">
-        <v>6931325</v>
+        <v>6931482</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3719,7 +3716,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3729,12 +3726,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283250</v>
+        <v>125283609</v>
       </c>
       <c r="B28" t="n">
-        <v>57995</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3777,39 +3769,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589679</v>
+        <v>589655</v>
       </c>
       <c r="R28" t="n">
-        <v>6931418</v>
+        <v>6931459</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3841,7 +3828,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3851,7 +3838,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3878,10 +3865,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125283609</v>
+        <v>125284936</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3890,38 +3877,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589655</v>
+        <v>589486</v>
       </c>
       <c r="R29" t="n">
-        <v>6931459</v>
+        <v>6931494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3953,7 +3944,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3963,7 +3954,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3978,22 +3969,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125286321</v>
+        <v>125290551</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4006,39 +3997,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589560</v>
+        <v>589606</v>
       </c>
       <c r="R30" t="n">
-        <v>6931398</v>
+        <v>6931325</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4070,7 +4056,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4080,12 +4066,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4100,22 +4081,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125284804</v>
+        <v>125286102</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4124,31 +4105,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4157,10 +4138,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589522</v>
+        <v>589438</v>
       </c>
       <c r="R31" t="n">
-        <v>6931472</v>
+        <v>6931387</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4192,7 +4173,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4202,7 +4183,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4217,22 +4203,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125284251</v>
+        <v>125290527</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4245,26 +4231,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4273,10 +4260,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589508</v>
+        <v>589624</v>
       </c>
       <c r="R32" t="n">
-        <v>6931482</v>
+        <v>6931325</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4308,7 +4295,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4318,7 +4305,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4345,10 +4337,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125290551</v>
+        <v>125283801</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4361,34 +4353,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589606</v>
+        <v>589633</v>
       </c>
       <c r="R33" t="n">
-        <v>6931325</v>
+        <v>6931451</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4420,7 +4417,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4430,7 +4427,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4457,10 +4459,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125285242</v>
+        <v>125285776</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4469,43 +4471,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589459</v>
+        <v>589446</v>
       </c>
       <c r="R34" t="n">
-        <v>6931441</v>
+        <v>6931392</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4537,7 +4534,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,7 +4544,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4562,19 +4559,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125283801</v>
+        <v>125285099</v>
       </c>
       <c r="B35" t="n">
         <v>57513</v>
@@ -4619,10 +4616,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589633</v>
+        <v>589466</v>
       </c>
       <c r="R35" t="n">
-        <v>6931451</v>
+        <v>6931475</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4654,7 +4651,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,12 +4661,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4696,10 +4693,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125284988</v>
+        <v>125283936</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4708,30 +4705,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4740,10 +4738,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589474</v>
+        <v>589597</v>
       </c>
       <c r="R36" t="n">
-        <v>6931483</v>
+        <v>6931482</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4775,7 +4773,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4785,7 +4783,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4800,22 +4803,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125284312</v>
+        <v>125284988</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4828,27 +4831,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4857,10 +4859,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589522</v>
+        <v>589474</v>
       </c>
       <c r="R37" t="n">
-        <v>6931472</v>
+        <v>6931483</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4892,7 +4894,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4902,12 +4904,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4922,22 +4919,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125283953</v>
+        <v>125284432</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4950,26 +4947,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4978,10 +4976,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589633</v>
+        <v>589518</v>
       </c>
       <c r="R38" t="n">
-        <v>6931451</v>
+        <v>6931461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5013,7 +5011,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5023,7 +5021,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5038,12 +5041,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5167,10 +5170,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125284881</v>
+        <v>125287385</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5183,21 +5186,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5207,10 +5210,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589483</v>
+        <v>589447</v>
       </c>
       <c r="R40" t="n">
-        <v>6931476</v>
+        <v>6931328</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5242,7 +5245,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5252,7 +5255,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5279,10 +5282,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125287027</v>
+        <v>125284804</v>
       </c>
       <c r="B41" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5295,34 +5298,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589571</v>
+        <v>589522</v>
       </c>
       <c r="R41" t="n">
-        <v>6931323</v>
+        <v>6931472</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5354,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5364,7 +5372,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5391,10 +5399,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125284607</v>
+        <v>125283329</v>
       </c>
       <c r="B42" t="n">
-        <v>92326</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5403,35 +5411,31 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5440,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589522</v>
+        <v>589665</v>
       </c>
       <c r="R42" t="n">
-        <v>6931472</v>
+        <v>6931444</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5475,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5485,12 +5489,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5517,10 +5521,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125284936</v>
+        <v>125287027</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5529,42 +5533,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589486</v>
+        <v>589571</v>
       </c>
       <c r="R43" t="n">
-        <v>6931494</v>
+        <v>6931323</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5621,22 +5621,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125291148</v>
+        <v>125283192</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5645,31 +5645,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589727</v>
+        <v>589701</v>
       </c>
       <c r="R44" t="n">
-        <v>6931355</v>
+        <v>6931425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5755,7 +5755,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125316461</v>
+        <v>125316739</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5791,7 +5791,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589678</v>
+        <v>589717</v>
       </c>
       <c r="R45" t="n">
-        <v>6931231</v>
+        <v>6931235</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5989,10 +5989,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316811</v>
+        <v>125316951</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6005,34 +6005,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R47" t="n">
-        <v>6931206</v>
+        <v>6931248</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6064,7 +6069,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6074,7 +6079,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6101,10 +6111,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316951</v>
+        <v>125316811</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6117,39 +6127,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931248</v>
+        <v>6931206</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6181,7 +6186,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6191,12 +6196,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6223,7 +6223,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125316739</v>
+        <v>125316461</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6259,7 +6259,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589717</v>
+        <v>589678</v>
       </c>
       <c r="R49" t="n">
-        <v>6931235</v>
+        <v>6931231</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -2574,10 +2574,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125283973</v>
+        <v>125283205</v>
       </c>
       <c r="B18" t="n">
-        <v>91023</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2590,21 +2590,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1205</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589587</v>
+        <v>589702</v>
       </c>
       <c r="R18" t="n">
-        <v>6931481</v>
+        <v>6931407</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2686,10 +2686,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125284251</v>
+        <v>125283973</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,42 +2698,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589508</v>
+        <v>589587</v>
       </c>
       <c r="R19" t="n">
-        <v>6931482</v>
+        <v>6931481</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2761,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2771,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,22 +2786,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125283250</v>
+        <v>125284251</v>
       </c>
       <c r="B20" t="n">
-        <v>57995</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2818,27 +2814,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2847,10 +2842,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589679</v>
+        <v>589508</v>
       </c>
       <c r="R20" t="n">
-        <v>6931418</v>
+        <v>6931482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2882,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2892,7 +2887,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2907,22 +2902,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125285548</v>
+        <v>125286321</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2935,27 +2930,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2964,10 +2959,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589543</v>
+        <v>589560</v>
       </c>
       <c r="R21" t="n">
-        <v>6931382</v>
+        <v>6931398</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2999,7 +2994,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3009,7 +3004,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125283205</v>
+        <v>125285519</v>
       </c>
       <c r="B22" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,38 +3048,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589702</v>
+        <v>589515</v>
       </c>
       <c r="R22" t="n">
-        <v>6931407</v>
+        <v>6931442</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3111,7 +3116,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3121,7 +3126,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3148,7 +3158,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125286321</v>
+        <v>125286059</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3193,10 +3203,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589560</v>
+        <v>589552</v>
       </c>
       <c r="R23" t="n">
-        <v>6931398</v>
+        <v>6931425</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3228,7 +3238,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3238,7 +3248,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3270,10 +3280,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125285519</v>
+        <v>125283250</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57995</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3286,27 +3296,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3315,10 +3325,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589515</v>
+        <v>589679</v>
       </c>
       <c r="R24" t="n">
-        <v>6931442</v>
+        <v>6931418</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3350,7 +3360,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3360,12 +3370,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3392,10 +3397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125286059</v>
+        <v>125285548</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3408,27 +3413,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3437,10 +3442,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589552</v>
+        <v>589543</v>
       </c>
       <c r="R25" t="n">
-        <v>6931425</v>
+        <v>6931382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3472,7 +3477,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3482,12 +3487,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4693,10 +4693,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125283936</v>
+        <v>125284988</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4705,31 +4705,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4738,10 +4737,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589597</v>
+        <v>589474</v>
       </c>
       <c r="R36" t="n">
-        <v>6931482</v>
+        <v>6931483</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4773,7 +4772,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4783,12 +4782,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4803,22 +4797,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125284988</v>
+        <v>125284432</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4831,26 +4825,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4859,10 +4854,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589474</v>
+        <v>589518</v>
       </c>
       <c r="R37" t="n">
-        <v>6931483</v>
+        <v>6931461</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4894,7 +4889,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4904,7 +4899,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,22 +4919,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125284432</v>
+        <v>125283936</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4943,31 +4943,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4976,10 +4976,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589518</v>
+        <v>589597</v>
       </c>
       <c r="R38" t="n">
-        <v>6931461</v>
+        <v>6931482</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5399,10 +5399,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125283329</v>
+        <v>125287027</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5411,43 +5411,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589665</v>
+        <v>589571</v>
       </c>
       <c r="R42" t="n">
-        <v>6931444</v>
+        <v>6931323</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5479,7 +5474,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,12 +5484,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5521,10 +5511,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125287027</v>
+        <v>125283329</v>
       </c>
       <c r="B43" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5533,38 +5523,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589571</v>
+        <v>589665</v>
       </c>
       <c r="R43" t="n">
-        <v>6931323</v>
+        <v>6931444</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5596,7 +5591,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5606,7 +5601,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283953</v>
+        <v>125283250</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57995</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589633</v>
+        <v>589679</v>
       </c>
       <c r="R2" t="n">
-        <v>6931451</v>
+        <v>6931418</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125285242</v>
+        <v>125284424</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,16 +808,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589459</v>
+        <v>589508</v>
       </c>
       <c r="R3" t="n">
-        <v>6931441</v>
+        <v>6931482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125285335</v>
+        <v>125285099</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -953,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589527</v>
+        <v>589466</v>
       </c>
       <c r="R4" t="n">
-        <v>6931442</v>
+        <v>6931475</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125285367</v>
+        <v>125284936</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,38 +1043,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589527</v>
+        <v>589486</v>
       </c>
       <c r="R5" t="n">
-        <v>6931442</v>
+        <v>6931494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125283173</v>
+        <v>125283192</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,31 +1159,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589711</v>
+        <v>589701</v>
       </c>
       <c r="R6" t="n">
-        <v>6931414</v>
+        <v>6931425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,14 +1225,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125284881</v>
+        <v>125283973</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1281,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589483</v>
+        <v>589587</v>
       </c>
       <c r="R7" t="n">
-        <v>6931476</v>
+        <v>6931481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125286223</v>
+        <v>125284432</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,16 +1397,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1411,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589552</v>
+        <v>589518</v>
       </c>
       <c r="R8" t="n">
-        <v>6931425</v>
+        <v>6931461</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125285600</v>
+        <v>125285548</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,34 +1519,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589438</v>
+        <v>589543</v>
       </c>
       <c r="R9" t="n">
-        <v>6931387</v>
+        <v>6931382</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125291148</v>
+        <v>125287385</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,16 +1636,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1629,21 +1654,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589727</v>
+        <v>589447</v>
       </c>
       <c r="R10" t="n">
-        <v>6931355</v>
+        <v>6931328</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,12 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,19 +1720,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125283860</v>
+        <v>125286793</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1762,10 +1777,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589606</v>
+        <v>589614</v>
       </c>
       <c r="R11" t="n">
-        <v>6931471</v>
+        <v>6931331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1839,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125284607</v>
+        <v>125285519</v>
       </c>
       <c r="B12" t="n">
-        <v>92326</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1851,35 +1866,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1888,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589522</v>
+        <v>589515</v>
       </c>
       <c r="R12" t="n">
-        <v>6931472</v>
+        <v>6931442</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1933,12 +1944,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125286606</v>
+        <v>125285335</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,16 +1992,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2010,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589602</v>
+        <v>589527</v>
       </c>
       <c r="R13" t="n">
-        <v>6931356</v>
+        <v>6931442</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2056,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2066,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,10 +2098,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125286793</v>
+        <v>125286223</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,16 +2114,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2127,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589614</v>
+        <v>589552</v>
       </c>
       <c r="R14" t="n">
-        <v>6931331</v>
+        <v>6931425</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2178,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,12 +2188,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,10 +2215,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125284312</v>
+        <v>125287027</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,43 +2227,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589522</v>
+        <v>589571</v>
       </c>
       <c r="R15" t="n">
-        <v>6931472</v>
+        <v>6931323</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2290,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2300,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125283515</v>
+        <v>125286102</v>
       </c>
       <c r="B16" t="n">
-        <v>92326</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,35 +2339,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2375,10 +2372,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589701</v>
+        <v>589438</v>
       </c>
       <c r="R16" t="n">
-        <v>6931425</v>
+        <v>6931387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,12 +2417,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2452,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125285293</v>
+        <v>125286606</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2468,16 +2465,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2497,10 +2494,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589459</v>
+        <v>589602</v>
       </c>
       <c r="R17" t="n">
-        <v>6931441</v>
+        <v>6931356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2529,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,12 +2539,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder Järpe</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,22 +2554,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125283205</v>
+        <v>125290551</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,25 +2578,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2614,10 +2606,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589702</v>
+        <v>589606</v>
       </c>
       <c r="R18" t="n">
-        <v>6931407</v>
+        <v>6931325</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2649,7 +2641,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2659,7 +2651,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2674,22 +2666,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125283973</v>
+        <v>125291148</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2698,38 +2690,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589587</v>
+        <v>589727</v>
       </c>
       <c r="R19" t="n">
-        <v>6931481</v>
+        <v>6931355</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2761,7 +2758,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2771,7 +2768,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,22 +2788,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125284251</v>
+        <v>125285293</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,26 +2816,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2842,10 +2845,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589508</v>
+        <v>589459</v>
       </c>
       <c r="R20" t="n">
-        <v>6931482</v>
+        <v>6931441</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2877,7 +2880,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2887,7 +2890,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,10 +2922,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125286321</v>
+        <v>125284607</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>92326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2926,31 +2934,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2959,10 +2971,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589560</v>
+        <v>589522</v>
       </c>
       <c r="R21" t="n">
-        <v>6931398</v>
+        <v>6931472</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2994,7 +3006,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3004,12 +3016,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,7 +3048,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125285519</v>
+        <v>125284312</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3081,10 +3093,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589515</v>
+        <v>589522</v>
       </c>
       <c r="R22" t="n">
-        <v>6931442</v>
+        <v>6931472</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3116,7 +3128,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3126,7 +3138,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3158,7 +3170,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125286059</v>
+        <v>125283801</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3203,10 +3215,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589552</v>
+        <v>589633</v>
       </c>
       <c r="R23" t="n">
-        <v>6931425</v>
+        <v>6931451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,7 +3250,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3248,12 +3260,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3268,22 +3280,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125283250</v>
+        <v>125286321</v>
       </c>
       <c r="B24" t="n">
-        <v>57995</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3296,27 +3308,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103018</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3325,10 +3337,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589679</v>
+        <v>589560</v>
       </c>
       <c r="R24" t="n">
-        <v>6931418</v>
+        <v>6931398</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3360,7 +3372,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,7 +3382,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3397,10 +3414,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125285548</v>
+        <v>125283205</v>
       </c>
       <c r="B25" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3409,43 +3426,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589543</v>
+        <v>589702</v>
       </c>
       <c r="R25" t="n">
-        <v>6931382</v>
+        <v>6931407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3477,7 +3489,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3499,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3514,10 +3526,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125284981</v>
+        <v>125284804</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3526,31 +3538,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3559,10 +3571,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589475</v>
+        <v>589522</v>
       </c>
       <c r="R26" t="n">
-        <v>6931470</v>
+        <v>6931472</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3594,7 +3606,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3604,12 +3616,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3636,10 +3643,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125284424</v>
+        <v>125284981</v>
       </c>
       <c r="B27" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,16 +3659,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3681,10 +3688,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589508</v>
+        <v>589475</v>
       </c>
       <c r="R27" t="n">
-        <v>6931482</v>
+        <v>6931470</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3716,7 +3723,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3726,7 +3733,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3741,22 +3753,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283609</v>
+        <v>125283173</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3769,34 +3781,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589655</v>
+        <v>589711</v>
       </c>
       <c r="R28" t="n">
-        <v>6931459</v>
+        <v>6931414</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3826,19 +3843,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:17</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3865,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125284936</v>
+        <v>125285367</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3877,42 +3889,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589486</v>
+        <v>589527</v>
       </c>
       <c r="R29" t="n">
-        <v>6931494</v>
+        <v>6931442</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3944,7 +3952,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3954,7 +3962,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3969,22 +3977,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125290551</v>
+        <v>125284367</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3997,21 +4005,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4021,10 +4029,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589606</v>
+        <v>589508</v>
       </c>
       <c r="R30" t="n">
-        <v>6931325</v>
+        <v>6931482</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4056,7 +4064,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4066,7 +4074,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,10 +4106,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125286102</v>
+        <v>125283609</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4109,39 +4122,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589438</v>
+        <v>589655</v>
       </c>
       <c r="R31" t="n">
-        <v>6931387</v>
+        <v>6931459</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4173,7 +4181,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4183,12 +4191,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4203,22 +4206,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125290527</v>
+        <v>125284251</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4231,27 +4234,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4260,10 +4262,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589624</v>
+        <v>589508</v>
       </c>
       <c r="R32" t="n">
-        <v>6931325</v>
+        <v>6931482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4295,7 +4297,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4305,12 +4307,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4337,10 +4334,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125283801</v>
+        <v>125284881</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4353,39 +4350,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589633</v>
+        <v>589483</v>
       </c>
       <c r="R33" t="n">
-        <v>6931451</v>
+        <v>6931476</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4417,7 +4409,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4427,12 +4419,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4447,22 +4434,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125285776</v>
+        <v>125283515</v>
       </c>
       <c r="B34" t="n">
-        <v>91023</v>
+        <v>92326</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4475,34 +4462,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1205</v>
+        <v>5964</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589446</v>
+        <v>589701</v>
       </c>
       <c r="R34" t="n">
-        <v>6931392</v>
+        <v>6931425</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4534,7 +4530,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4544,7 +4540,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4559,22 +4560,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125285099</v>
+        <v>125285600</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4587,39 +4588,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589466</v>
+        <v>589438</v>
       </c>
       <c r="R35" t="n">
-        <v>6931475</v>
+        <v>6931387</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4651,7 +4647,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4661,12 +4657,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4693,10 +4684,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125284988</v>
+        <v>125290527</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4709,26 +4700,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4737,10 +4729,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589474</v>
+        <v>589624</v>
       </c>
       <c r="R36" t="n">
-        <v>6931483</v>
+        <v>6931325</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4772,7 +4764,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4782,7 +4774,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4809,7 +4806,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125284432</v>
+        <v>125283860</v>
       </c>
       <c r="B37" t="n">
         <v>57513</v>
@@ -4854,10 +4851,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589518</v>
+        <v>589606</v>
       </c>
       <c r="R37" t="n">
-        <v>6931461</v>
+        <v>6931471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4889,7 +4886,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4899,7 +4896,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4931,10 +4928,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125283936</v>
+        <v>125285776</v>
       </c>
       <c r="B38" t="n">
-        <v>56722</v>
+        <v>91023</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4947,39 +4944,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>1205</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589597</v>
+        <v>589446</v>
       </c>
       <c r="R38" t="n">
-        <v>6931482</v>
+        <v>6931392</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5011,7 +5003,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5021,12 +5013,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5053,10 +5040,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125284367</v>
+        <v>125284988</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5069,34 +5056,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589508</v>
+        <v>589474</v>
       </c>
       <c r="R39" t="n">
-        <v>6931482</v>
+        <v>6931483</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5128,7 +5119,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5138,12 +5129,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enormt mycket lunglav</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5170,10 +5156,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125287385</v>
+        <v>125286059</v>
       </c>
       <c r="B40" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5186,16 +5172,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5204,16 +5190,21 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589447</v>
+        <v>589552</v>
       </c>
       <c r="R40" t="n">
-        <v>6931328</v>
+        <v>6931425</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5245,7 +5236,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5255,7 +5246,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5282,10 +5278,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125284804</v>
+        <v>125285242</v>
       </c>
       <c r="B41" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5294,31 +5290,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5327,10 +5323,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589522</v>
+        <v>589459</v>
       </c>
       <c r="R41" t="n">
-        <v>6931472</v>
+        <v>6931441</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5362,7 +5358,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5368,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5387,22 +5383,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125287027</v>
+        <v>125283953</v>
       </c>
       <c r="B42" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5411,38 +5407,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589571</v>
+        <v>589633</v>
       </c>
       <c r="R42" t="n">
-        <v>6931323</v>
+        <v>6931451</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5499,12 +5499,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125283192</v>
+        <v>125283936</v>
       </c>
       <c r="B44" t="n">
         <v>56722</v>
@@ -5669,7 +5669,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589701</v>
+        <v>589597</v>
       </c>
       <c r="R44" t="n">
-        <v>6931425</v>
+        <v>6931482</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5743,12 +5743,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316757</v>
+        <v>125316461</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5893,34 +5893,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589713</v>
+        <v>589678</v>
       </c>
       <c r="R46" t="n">
-        <v>6931246</v>
+        <v>6931231</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5952,7 +5957,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5962,7 +5967,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6223,10 +6233,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125316461</v>
+        <v>125316757</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6239,39 +6249,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589678</v>
+        <v>589713</v>
       </c>
       <c r="R49" t="n">
-        <v>6931231</v>
+        <v>6931246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6303,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6313,12 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125283973</v>
+        <v>125285548</v>
       </c>
       <c r="B7" t="n">
-        <v>91023</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,38 +1281,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1205</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589587</v>
+        <v>589543</v>
       </c>
       <c r="R7" t="n">
-        <v>6931481</v>
+        <v>6931382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125284432</v>
+        <v>125283973</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91023</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,43 +1398,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589518</v>
+        <v>589587</v>
       </c>
       <c r="R8" t="n">
-        <v>6931461</v>
+        <v>6931481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125285548</v>
+        <v>125284432</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,27 +1514,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1548,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589543</v>
+        <v>589518</v>
       </c>
       <c r="R9" t="n">
-        <v>6931382</v>
+        <v>6931461</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1976,10 +1976,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125285335</v>
+        <v>125286223</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,16 +1992,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589527</v>
+        <v>589552</v>
       </c>
       <c r="R13" t="n">
-        <v>6931442</v>
+        <v>6931425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2066,12 +2066,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,10 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125286223</v>
+        <v>125285335</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,16 +2109,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2143,10 +2138,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589552</v>
+        <v>589527</v>
       </c>
       <c r="R14" t="n">
-        <v>6931425</v>
+        <v>6931442</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,7 +2173,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2188,7 +2183,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3292,10 +3292,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125286321</v>
+        <v>125283205</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3304,43 +3304,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589560</v>
+        <v>589702</v>
       </c>
       <c r="R24" t="n">
-        <v>6931398</v>
+        <v>6931407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3372,7 +3367,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3382,12 +3377,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3414,10 +3404,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125283205</v>
+        <v>125286321</v>
       </c>
       <c r="B25" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3426,38 +3416,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589702</v>
+        <v>589560</v>
       </c>
       <c r="R25" t="n">
-        <v>6931407</v>
+        <v>6931398</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3489,7 +3484,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3499,7 +3494,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316951</v>
+        <v>125316811</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6015,39 +6015,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R47" t="n">
-        <v>6931248</v>
+        <v>6931206</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6079,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6089,12 +6084,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6121,10 +6111,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316811</v>
+        <v>125316951</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6137,34 +6127,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R48" t="n">
-        <v>6931206</v>
+        <v>6931248</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6196,7 +6191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6206,7 +6201,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283250</v>
+        <v>125283973</v>
       </c>
       <c r="B2" t="n">
-        <v>57995</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589679</v>
+        <v>589587</v>
       </c>
       <c r="R2" t="n">
-        <v>6931418</v>
+        <v>6931481</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125284424</v>
+        <v>125284607</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>92326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,31 +799,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589508</v>
+        <v>589522</v>
       </c>
       <c r="R3" t="n">
-        <v>6931482</v>
+        <v>6931472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125285099</v>
+        <v>125284424</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -954,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589466</v>
+        <v>589508</v>
       </c>
       <c r="R4" t="n">
-        <v>6931475</v>
+        <v>6931482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125284936</v>
+        <v>125285367</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,42 +1042,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589486</v>
+        <v>589527</v>
       </c>
       <c r="R5" t="n">
-        <v>6931494</v>
+        <v>6931442</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,19 +1130,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125283192</v>
+        <v>125284804</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1183,7 +1178,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1192,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589701</v>
+        <v>589522</v>
       </c>
       <c r="R6" t="n">
-        <v>6931425</v>
+        <v>6931472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1247,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125285548</v>
+        <v>125284251</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,27 +1275,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589543</v>
+        <v>589508</v>
       </c>
       <c r="R7" t="n">
-        <v>6931382</v>
+        <v>6931482</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125283973</v>
+        <v>125283953</v>
       </c>
       <c r="B8" t="n">
-        <v>91023</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,38 +1387,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589587</v>
+        <v>589633</v>
       </c>
       <c r="R8" t="n">
-        <v>6931481</v>
+        <v>6931451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1479,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125284432</v>
+        <v>125283515</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>92326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,31 +1503,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1543,10 +1540,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589518</v>
+        <v>589701</v>
       </c>
       <c r="R9" t="n">
-        <v>6931461</v>
+        <v>6931425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,12 +1585,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,22 +1605,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125287385</v>
+        <v>125285519</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,16 +1633,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1654,16 +1651,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589447</v>
+        <v>589515</v>
       </c>
       <c r="R10" t="n">
-        <v>6931328</v>
+        <v>6931442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1697,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1707,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,7 +1739,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125286793</v>
+        <v>125285099</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1777,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589614</v>
+        <v>589466</v>
       </c>
       <c r="R11" t="n">
-        <v>6931331</v>
+        <v>6931475</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,12 +1829,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,19 +1849,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125285519</v>
+        <v>125283860</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1899,10 +1906,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589515</v>
+        <v>589606</v>
       </c>
       <c r="R12" t="n">
-        <v>6931442</v>
+        <v>6931471</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1951,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1976,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125286223</v>
+        <v>125286059</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,16 +1999,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2056,7 +2063,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2066,7 +2073,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2105,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125285335</v>
+        <v>125283936</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,31 +2117,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2138,10 +2150,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589527</v>
+        <v>589597</v>
       </c>
       <c r="R14" t="n">
-        <v>6931442</v>
+        <v>6931482</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2173,7 +2185,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2183,12 +2195,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,10 +2227,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125287027</v>
+        <v>125283192</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2231,34 +2243,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589571</v>
+        <v>589701</v>
       </c>
       <c r="R15" t="n">
-        <v>6931323</v>
+        <v>6931425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2307,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2300,7 +2317,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2315,22 +2337,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125286102</v>
+        <v>125287385</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,16 +2365,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2361,21 +2383,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589438</v>
+        <v>589447</v>
       </c>
       <c r="R16" t="n">
-        <v>6931387</v>
+        <v>6931328</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2424,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,12 +2434,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,22 +2449,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125286606</v>
+        <v>125285776</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>91023</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,43 +2473,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589602</v>
+        <v>589446</v>
       </c>
       <c r="R17" t="n">
-        <v>6931356</v>
+        <v>6931392</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2529,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2539,7 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2678,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125291148</v>
+        <v>125287027</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2690,43 +2697,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589727</v>
+        <v>589571</v>
       </c>
       <c r="R19" t="n">
-        <v>6931355</v>
+        <v>6931323</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2758,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2768,12 +2770,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,22 +2785,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125285293</v>
+        <v>125283205</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2812,43 +2809,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589459</v>
+        <v>589702</v>
       </c>
       <c r="R20" t="n">
-        <v>6931441</v>
+        <v>6931407</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2880,7 +2872,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2890,12 +2882,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Fjäder Järpe</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2910,22 +2897,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125284607</v>
+        <v>125284367</v>
       </c>
       <c r="B21" t="n">
-        <v>92326</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2934,47 +2921,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589522</v>
+        <v>589508</v>
       </c>
       <c r="R21" t="n">
-        <v>6931472</v>
+        <v>6931482</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3006,7 +2984,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,12 +2994,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,22 +3014,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125284312</v>
+        <v>125285293</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3064,16 +3042,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3093,10 +3071,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589522</v>
+        <v>589459</v>
       </c>
       <c r="R22" t="n">
-        <v>6931472</v>
+        <v>6931441</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3128,7 +3106,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3138,12 +3116,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3158,22 +3136,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125283801</v>
+        <v>125284988</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3186,27 +3164,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3215,10 +3192,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589633</v>
+        <v>589474</v>
       </c>
       <c r="R23" t="n">
-        <v>6931451</v>
+        <v>6931483</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3250,7 +3227,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3260,12 +3237,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3292,10 +3264,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125283205</v>
+        <v>125285335</v>
       </c>
       <c r="B24" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3304,38 +3276,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589702</v>
+        <v>589527</v>
       </c>
       <c r="R24" t="n">
-        <v>6931407</v>
+        <v>6931442</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3367,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3377,7 +3354,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3404,7 +3386,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125286321</v>
+        <v>125284981</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3449,10 +3431,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589560</v>
+        <v>589475</v>
       </c>
       <c r="R25" t="n">
-        <v>6931398</v>
+        <v>6931470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3484,7 +3466,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3494,12 +3476,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3526,10 +3508,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125284804</v>
+        <v>125285600</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3538,43 +3520,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589522</v>
+        <v>589438</v>
       </c>
       <c r="R26" t="n">
-        <v>6931472</v>
+        <v>6931387</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3606,7 +3583,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3616,7 +3593,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,22 +3608,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125284981</v>
+        <v>125283609</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3659,39 +3636,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589475</v>
+        <v>589655</v>
       </c>
       <c r="R27" t="n">
-        <v>6931470</v>
+        <v>6931459</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3723,7 +3695,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3733,12 +3705,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,10 +3732,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283173</v>
+        <v>125286606</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3781,16 +3748,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3810,10 +3777,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589711</v>
+        <v>589602</v>
       </c>
       <c r="R28" t="n">
-        <v>6931414</v>
+        <v>6931356</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3843,14 +3810,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,10 +3849,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125285367</v>
+        <v>125284936</v>
       </c>
       <c r="B29" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,38 +3861,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589527</v>
+        <v>589486</v>
       </c>
       <c r="R29" t="n">
-        <v>6931442</v>
+        <v>6931494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3952,7 +3928,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3962,7 +3938,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,22 +3953,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125284367</v>
+        <v>125286321</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4005,34 +3981,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589508</v>
+        <v>589560</v>
       </c>
       <c r="R30" t="n">
-        <v>6931482</v>
+        <v>6931398</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4064,7 +4045,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4074,12 +4055,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enormt mycket lunglav</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4094,22 +4075,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125283609</v>
+        <v>125291148</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4122,34 +4103,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589655</v>
+        <v>589727</v>
       </c>
       <c r="R31" t="n">
-        <v>6931459</v>
+        <v>6931355</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4181,7 +4167,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4191,7 +4177,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4206,22 +4197,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125284251</v>
+        <v>125283250</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57995</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4234,26 +4225,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103018</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4262,10 +4254,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589508</v>
+        <v>589679</v>
       </c>
       <c r="R32" t="n">
-        <v>6931482</v>
+        <v>6931418</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4297,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4307,7 +4299,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4322,22 +4314,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125284881</v>
+        <v>125283801</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4350,34 +4342,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589483</v>
+        <v>589633</v>
       </c>
       <c r="R33" t="n">
-        <v>6931476</v>
+        <v>6931451</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4409,7 +4406,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4419,7 +4416,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4434,22 +4436,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125283515</v>
+        <v>125284432</v>
       </c>
       <c r="B34" t="n">
-        <v>92326</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4458,35 +4460,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4495,10 +4493,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589701</v>
+        <v>589518</v>
       </c>
       <c r="R34" t="n">
-        <v>6931425</v>
+        <v>6931461</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4530,7 +4528,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4540,12 +4538,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4560,22 +4558,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125285600</v>
+        <v>125290527</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4588,34 +4586,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589438</v>
+        <v>589624</v>
       </c>
       <c r="R35" t="n">
-        <v>6931387</v>
+        <v>6931325</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4647,7 +4650,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4657,7 +4660,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4684,7 +4692,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125290527</v>
+        <v>125286793</v>
       </c>
       <c r="B36" t="n">
         <v>57513</v>
@@ -4729,10 +4737,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589624</v>
+        <v>589614</v>
       </c>
       <c r="R36" t="n">
-        <v>6931325</v>
+        <v>6931331</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4764,7 +4772,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4774,12 +4782,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4794,22 +4802,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125283860</v>
+        <v>125284881</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4822,39 +4830,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589606</v>
+        <v>589483</v>
       </c>
       <c r="R37" t="n">
-        <v>6931471</v>
+        <v>6931476</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4886,7 +4889,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4896,12 +4899,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4928,10 +4926,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125285776</v>
+        <v>125285242</v>
       </c>
       <c r="B38" t="n">
-        <v>91023</v>
+        <v>57529</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4940,38 +4938,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589446</v>
+        <v>589459</v>
       </c>
       <c r="R38" t="n">
-        <v>6931392</v>
+        <v>6931441</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5003,7 +5006,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5013,7 +5016,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5028,22 +5031,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125284988</v>
+        <v>125286223</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5056,26 +5059,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5084,10 +5088,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589474</v>
+        <v>589552</v>
       </c>
       <c r="R39" t="n">
-        <v>6931483</v>
+        <v>6931425</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5119,7 +5123,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5129,7 +5133,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5144,19 +5148,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125286059</v>
+        <v>125284312</v>
       </c>
       <c r="B40" t="n">
         <v>57513</v>
@@ -5201,10 +5205,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589552</v>
+        <v>589522</v>
       </c>
       <c r="R40" t="n">
-        <v>6931425</v>
+        <v>6931472</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5236,7 +5240,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5246,7 +5250,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -5278,10 +5282,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125285242</v>
+        <v>125285548</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5294,27 +5298,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5323,10 +5327,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589459</v>
+        <v>589543</v>
       </c>
       <c r="R41" t="n">
-        <v>6931441</v>
+        <v>6931382</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5368,7 +5372,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5383,22 +5387,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125283953</v>
+        <v>125286102</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5411,26 +5415,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5439,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589633</v>
+        <v>589438</v>
       </c>
       <c r="R42" t="n">
-        <v>6931451</v>
+        <v>6931387</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5474,7 +5479,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5484,7 +5489,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5511,7 +5521,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125283329</v>
+        <v>125283173</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5556,10 +5566,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589665</v>
+        <v>589711</v>
       </c>
       <c r="R43" t="n">
-        <v>6931444</v>
+        <v>6931414</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5589,24 +5599,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:06</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:06</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5633,10 +5633,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125283936</v>
+        <v>125283329</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5645,31 +5645,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589597</v>
+        <v>589665</v>
       </c>
       <c r="R44" t="n">
-        <v>6931482</v>
+        <v>6931444</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5755,7 +5755,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R45" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316811</v>
+        <v>125316757</v>
       </c>
       <c r="B47" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6015,21 +6015,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589713</v>
       </c>
       <c r="R47" t="n">
-        <v>6931206</v>
+        <v>6931246</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6111,7 +6111,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6233,10 +6233,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125316757</v>
+        <v>125316811</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6249,21 +6249,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589713</v>
+        <v>589717</v>
       </c>
       <c r="R49" t="n">
-        <v>6931246</v>
+        <v>6931206</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283973</v>
+        <v>125283936</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>56836</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589587</v>
+        <v>589597</v>
       </c>
       <c r="R2" t="n">
-        <v>6931481</v>
+        <v>6931482</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125284607</v>
+        <v>125283860</v>
       </c>
       <c r="B3" t="n">
-        <v>92326</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,35 +809,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589522</v>
+        <v>589606</v>
       </c>
       <c r="R3" t="n">
-        <v>6931472</v>
+        <v>6931471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125284424</v>
+        <v>125283609</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589508</v>
+        <v>589655</v>
       </c>
       <c r="R4" t="n">
-        <v>6931482</v>
+        <v>6931459</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125285367</v>
+        <v>125284367</v>
       </c>
       <c r="B5" t="n">
-        <v>105117</v>
+        <v>80028</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,25 +1043,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589527</v>
+        <v>589508</v>
       </c>
       <c r="R5" t="n">
-        <v>6931442</v>
+        <v>6931482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125284804</v>
+        <v>125286321</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,31 +1160,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1187,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589522</v>
+        <v>589560</v>
       </c>
       <c r="R6" t="n">
-        <v>6931472</v>
+        <v>6931398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125284251</v>
+        <v>125290527</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,26 +1286,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1303,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589508</v>
+        <v>589624</v>
       </c>
       <c r="R7" t="n">
-        <v>6931482</v>
+        <v>6931325</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125283953</v>
+        <v>125285776</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91177</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,42 +1404,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589633</v>
+        <v>589446</v>
       </c>
       <c r="R8" t="n">
-        <v>6931451</v>
+        <v>6931392</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,22 +1492,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125283515</v>
+        <v>125283250</v>
       </c>
       <c r="B9" t="n">
-        <v>92326</v>
+        <v>58111</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,35 +1516,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>103018</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1540,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589701</v>
+        <v>589679</v>
       </c>
       <c r="R9" t="n">
-        <v>6931425</v>
+        <v>6931418</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,12 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,22 +1609,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125285519</v>
+        <v>125284432</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589515</v>
+        <v>589518</v>
       </c>
       <c r="R10" t="n">
-        <v>6931442</v>
+        <v>6931461</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1697,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1707,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1739,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125285099</v>
+        <v>125287385</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,16 +1759,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1773,21 +1777,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589466</v>
+        <v>589447</v>
       </c>
       <c r="R11" t="n">
-        <v>6931475</v>
+        <v>6931328</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,12 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,22 +1843,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125283860</v>
+        <v>125284981</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1906,10 +1900,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589606</v>
+        <v>589475</v>
       </c>
       <c r="R12" t="n">
-        <v>6931471</v>
+        <v>6931470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,12 +1945,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125286059</v>
+        <v>125285367</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>105293</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,43 +1989,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589552</v>
+        <v>589527</v>
       </c>
       <c r="R13" t="n">
-        <v>6931425</v>
+        <v>6931442</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2073,12 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2105,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125283936</v>
+        <v>125284936</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2117,31 +2101,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2150,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589597</v>
+        <v>589486</v>
       </c>
       <c r="R14" t="n">
-        <v>6931482</v>
+        <v>6931494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2195,12 +2178,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,22 +2193,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125283192</v>
+        <v>125286102</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2239,31 +2217,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2272,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589701</v>
+        <v>589438</v>
       </c>
       <c r="R15" t="n">
-        <v>6931425</v>
+        <v>6931387</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2307,7 +2285,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2317,12 +2295,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125287385</v>
+        <v>125285335</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2365,16 +2343,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2383,16 +2361,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589447</v>
+        <v>589527</v>
       </c>
       <c r="R16" t="n">
-        <v>6931328</v>
+        <v>6931442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2424,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,7 +2417,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,10 +2449,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125285776</v>
+        <v>125285242</v>
       </c>
       <c r="B17" t="n">
-        <v>91023</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,38 +2461,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589446</v>
+        <v>589459</v>
       </c>
       <c r="R17" t="n">
-        <v>6931392</v>
+        <v>6931441</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,7 +2529,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2539,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,22 +2554,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125290551</v>
+        <v>125284424</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>56828</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,34 +2582,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589606</v>
+        <v>589508</v>
       </c>
       <c r="R18" t="n">
-        <v>6931325</v>
+        <v>6931482</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2648,7 +2646,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2656,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2685,10 +2683,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125287027</v>
+        <v>125284312</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,38 +2695,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589571</v>
+        <v>589522</v>
       </c>
       <c r="R19" t="n">
-        <v>6931323</v>
+        <v>6931472</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2760,7 +2763,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,7 +2773,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2797,10 +2805,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125283205</v>
+        <v>125285600</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>80028</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,25 +2817,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2837,10 +2845,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589702</v>
+        <v>589438</v>
       </c>
       <c r="R20" t="n">
-        <v>6931407</v>
+        <v>6931387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2872,7 +2880,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2882,7 +2890,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,22 +2905,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125284367</v>
+        <v>125284607</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>92482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2921,38 +2929,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589508</v>
+        <v>589522</v>
       </c>
       <c r="R21" t="n">
-        <v>6931482</v>
+        <v>6931472</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2984,7 +3001,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2994,12 +3011,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enormt mycket lunglav</t>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,22 +3031,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125285293</v>
+        <v>125286793</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3042,16 +3059,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3071,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589459</v>
+        <v>589614</v>
       </c>
       <c r="R22" t="n">
-        <v>6931441</v>
+        <v>6931331</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3106,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3116,12 +3133,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Fjäder Järpe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,22 +3153,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125284988</v>
+        <v>125284881</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3164,38 +3181,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589474</v>
+        <v>589483</v>
       </c>
       <c r="R23" t="n">
-        <v>6931483</v>
+        <v>6931476</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3227,7 +3240,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3237,7 +3250,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3252,22 +3265,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125285335</v>
+        <v>125286223</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3280,16 +3293,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3309,10 +3322,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589527</v>
+        <v>589552</v>
       </c>
       <c r="R24" t="n">
-        <v>6931442</v>
+        <v>6931425</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3344,7 +3357,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,12 +3367,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3386,10 +3394,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125284981</v>
+        <v>125283205</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>97147</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3398,43 +3406,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589475</v>
+        <v>589702</v>
       </c>
       <c r="R25" t="n">
-        <v>6931470</v>
+        <v>6931407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3466,7 +3469,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3476,12 +3479,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3508,10 +3506,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125285600</v>
+        <v>125283192</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>56836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3520,38 +3518,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589438</v>
+        <v>589701</v>
       </c>
       <c r="R26" t="n">
-        <v>6931387</v>
+        <v>6931425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3583,7 +3586,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3593,7 +3596,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3620,10 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125283609</v>
+        <v>125283801</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3636,34 +3644,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589655</v>
+        <v>589633</v>
       </c>
       <c r="R27" t="n">
-        <v>6931459</v>
+        <v>6931451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3695,7 +3708,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3705,7 +3718,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3720,22 +3738,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125286606</v>
+        <v>125285519</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3748,16 +3766,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3777,10 +3795,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589602</v>
+        <v>589515</v>
       </c>
       <c r="R28" t="n">
-        <v>6931356</v>
+        <v>6931442</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3812,7 +3830,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3822,7 +3840,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3849,10 +3872,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125284936</v>
+        <v>125285548</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57793</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3861,30 +3884,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3893,10 +3917,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589486</v>
+        <v>589543</v>
       </c>
       <c r="R29" t="n">
-        <v>6931494</v>
+        <v>6931382</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3928,7 +3952,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3938,7 +3962,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3953,22 +3977,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125286321</v>
+        <v>125286606</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3981,16 +4005,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4010,10 +4034,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589560</v>
+        <v>589602</v>
       </c>
       <c r="R30" t="n">
-        <v>6931398</v>
+        <v>6931356</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4045,7 +4069,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4055,12 +4079,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4087,10 +4106,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125291148</v>
+        <v>125283953</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4103,27 +4122,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4132,10 +4150,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589727</v>
+        <v>589633</v>
       </c>
       <c r="R31" t="n">
-        <v>6931355</v>
+        <v>6931451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4167,7 +4185,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4177,12 +4195,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4209,10 +4222,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125283250</v>
+        <v>125284251</v>
       </c>
       <c r="B32" t="n">
-        <v>57995</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4225,27 +4238,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4254,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589679</v>
+        <v>589508</v>
       </c>
       <c r="R32" t="n">
-        <v>6931418</v>
+        <v>6931482</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4289,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,7 +4311,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4314,22 +4326,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125283801</v>
+        <v>125285099</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4371,10 +4383,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589633</v>
+        <v>589466</v>
       </c>
       <c r="R33" t="n">
-        <v>6931451</v>
+        <v>6931475</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4406,7 +4418,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4416,12 +4428,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4448,10 +4460,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125284432</v>
+        <v>125285293</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>56828</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4464,16 +4476,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4493,10 +4505,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589518</v>
+        <v>589459</v>
       </c>
       <c r="R34" t="n">
-        <v>6931461</v>
+        <v>6931441</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4528,7 +4540,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4538,12 +4550,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4558,22 +4570,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125290527</v>
+        <v>125291148</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4615,10 +4627,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589624</v>
+        <v>589727</v>
       </c>
       <c r="R35" t="n">
-        <v>6931325</v>
+        <v>6931355</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4650,7 +4662,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4660,7 +4672,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4692,10 +4704,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125286793</v>
+        <v>125284988</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4708,27 +4720,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4737,10 +4748,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589614</v>
+        <v>589474</v>
       </c>
       <c r="R36" t="n">
-        <v>6931331</v>
+        <v>6931483</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4772,7 +4783,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4782,12 +4793,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4802,22 +4808,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125284881</v>
+        <v>125286059</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4830,34 +4836,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589483</v>
+        <v>589552</v>
       </c>
       <c r="R37" t="n">
-        <v>6931476</v>
+        <v>6931425</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4889,7 +4900,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4899,7 +4910,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4926,10 +4942,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125285242</v>
+        <v>125287027</v>
       </c>
       <c r="B38" t="n">
-        <v>57529</v>
+        <v>97147</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4938,43 +4954,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589459</v>
+        <v>589571</v>
       </c>
       <c r="R38" t="n">
-        <v>6931441</v>
+        <v>6931323</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5006,7 +5017,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5016,7 +5027,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5031,22 +5042,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125286223</v>
+        <v>125283515</v>
       </c>
       <c r="B39" t="n">
-        <v>57529</v>
+        <v>92482</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5055,31 +5066,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5088,7 +5103,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589552</v>
+        <v>589701</v>
       </c>
       <c r="R39" t="n">
         <v>6931425</v>
@@ -5123,7 +5138,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5133,7 +5148,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5148,22 +5168,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125284312</v>
+        <v>125284804</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>56836</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5172,31 +5192,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5240,7 +5260,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5250,12 +5270,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5282,10 +5297,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125285548</v>
+        <v>125283973</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>91177</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5294,43 +5309,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>1205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589543</v>
+        <v>589587</v>
       </c>
       <c r="R41" t="n">
-        <v>6931382</v>
+        <v>6931481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5362,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5372,7 +5382,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,10 +5409,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125286102</v>
+        <v>125283173</v>
       </c>
       <c r="B42" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5444,10 +5454,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589438</v>
+        <v>589711</v>
       </c>
       <c r="R42" t="n">
-        <v>6931387</v>
+        <v>6931414</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5477,24 +5487,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:57</t>
-        </is>
-      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5509,22 +5509,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125283173</v>
+        <v>125283329</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589711</v>
+        <v>589665</v>
       </c>
       <c r="R43" t="n">
-        <v>6931414</v>
+        <v>6931444</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5599,14 +5599,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5633,10 +5643,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125283329</v>
+        <v>125290551</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5649,39 +5659,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589665</v>
+        <v>589606</v>
       </c>
       <c r="R44" t="n">
-        <v>6931444</v>
+        <v>6931325</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5713,7 +5718,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5723,12 +5728,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5743,22 +5743,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125316951</v>
+        <v>125316461</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589777</v>
+        <v>589678</v>
       </c>
       <c r="R45" t="n">
-        <v>6931248</v>
+        <v>6931231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
@@ -5877,10 +5877,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316461</v>
+        <v>125316951</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589678</v>
+        <v>589777</v>
       </c>
       <c r="R46" t="n">
-        <v>6931231</v>
+        <v>6931248</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5999,10 +5999,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316757</v>
+        <v>125316739</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6015,34 +6015,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589713</v>
+        <v>589717</v>
       </c>
       <c r="R47" t="n">
-        <v>6931246</v>
+        <v>6931235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6074,7 +6079,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6084,7 +6089,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6111,10 +6121,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316739</v>
+        <v>125316757</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6127,39 +6137,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589717</v>
+        <v>589713</v>
       </c>
       <c r="R48" t="n">
-        <v>6931235</v>
+        <v>6931246</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6191,7 +6196,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6201,12 +6206,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6236,7 +6236,7 @@
         <v>125316811</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283936</v>
+        <v>125283609</v>
       </c>
       <c r="B2" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589597</v>
+        <v>589655</v>
       </c>
       <c r="R2" t="n">
-        <v>6931482</v>
+        <v>6931459</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125283860</v>
+        <v>125283936</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,31 +799,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589606</v>
+        <v>589597</v>
       </c>
       <c r="R3" t="n">
-        <v>6931471</v>
+        <v>6931482</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125283609</v>
+        <v>125283860</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589655</v>
+        <v>589606</v>
       </c>
       <c r="R4" t="n">
-        <v>6931459</v>
+        <v>6931471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125285600</v>
+        <v>125286793</v>
       </c>
       <c r="B20" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2821,34 +2821,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589438</v>
+        <v>589614</v>
       </c>
       <c r="R20" t="n">
-        <v>6931387</v>
+        <v>6931331</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2880,7 +2885,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2890,7 +2895,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,22 +2915,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125284607</v>
+        <v>125285600</v>
       </c>
       <c r="B21" t="n">
-        <v>92482</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,47 +2939,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589522</v>
+        <v>589438</v>
       </c>
       <c r="R21" t="n">
-        <v>6931472</v>
+        <v>6931387</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3001,7 +3002,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3011,12 +3012,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3031,22 +3027,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125286793</v>
+        <v>125284607</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
+        <v>92482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3055,31 +3051,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589614</v>
+        <v>589522</v>
       </c>
       <c r="R22" t="n">
-        <v>6931331</v>
+        <v>6931472</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283609</v>
+        <v>125283953</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
@@ -708,17 +708,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589655</v>
+        <v>589633</v>
       </c>
       <c r="R2" t="n">
-        <v>6931459</v>
+        <v>6931451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125283936</v>
+        <v>125286606</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589597</v>
+        <v>589602</v>
       </c>
       <c r="R3" t="n">
-        <v>6931482</v>
+        <v>6931356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125283860</v>
+        <v>125284251</v>
       </c>
       <c r="B4" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,27 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589606</v>
+        <v>589508</v>
       </c>
       <c r="R4" t="n">
-        <v>6931471</v>
+        <v>6931482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125284367</v>
+        <v>125290551</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,21 +1040,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589508</v>
+        <v>589606</v>
       </c>
       <c r="R5" t="n">
-        <v>6931482</v>
+        <v>6931325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enormt mycket lunglav</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125286321</v>
+        <v>125286102</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1193,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589560</v>
+        <v>589438</v>
       </c>
       <c r="R6" t="n">
-        <v>6931398</v>
+        <v>6931387</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1226,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125290527</v>
+        <v>125283515</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>92482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,31 +1270,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1307,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589624</v>
+        <v>589701</v>
       </c>
       <c r="R7" t="n">
-        <v>6931325</v>
+        <v>6931425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1342,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1352,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125285776</v>
+        <v>125285519</v>
       </c>
       <c r="B8" t="n">
-        <v>91177</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,38 +1396,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589446</v>
+        <v>589515</v>
       </c>
       <c r="R8" t="n">
-        <v>6931392</v>
+        <v>6931442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1474,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1506,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125283250</v>
+        <v>125284607</v>
       </c>
       <c r="B9" t="n">
-        <v>58111</v>
+        <v>92482</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1516,31 +1518,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103018</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589679</v>
+        <v>589522</v>
       </c>
       <c r="R9" t="n">
-        <v>6931418</v>
+        <v>6931472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1632,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125284432</v>
+        <v>125291148</v>
       </c>
       <c r="B10" t="n">
         <v>57635</v>
@@ -1666,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589518</v>
+        <v>589727</v>
       </c>
       <c r="R10" t="n">
-        <v>6931461</v>
+        <v>6931355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,12 +1722,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,22 +1742,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125287385</v>
+        <v>125284804</v>
       </c>
       <c r="B11" t="n">
-        <v>57632</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,38 +1766,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589447</v>
+        <v>589522</v>
       </c>
       <c r="R11" t="n">
-        <v>6931328</v>
+        <v>6931472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1834,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1844,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1871,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125284981</v>
+        <v>125284424</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,16 +1887,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1900,10 +1916,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589475</v>
+        <v>589508</v>
       </c>
       <c r="R12" t="n">
-        <v>6931470</v>
+        <v>6931482</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1951,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,12 +1961,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,22 +1976,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125285367</v>
+        <v>125286321</v>
       </c>
       <c r="B13" t="n">
-        <v>105293</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,38 +2000,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589527</v>
+        <v>589560</v>
       </c>
       <c r="R13" t="n">
-        <v>6931442</v>
+        <v>6931398</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,7 +2068,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2078,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,10 +2110,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125284936</v>
+        <v>125285600</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2101,42 +2122,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589486</v>
+        <v>589438</v>
       </c>
       <c r="R14" t="n">
-        <v>6931494</v>
+        <v>6931387</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2185,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2195,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,10 +2222,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125286102</v>
+        <v>125285242</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2221,16 +2238,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2250,10 +2267,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589438</v>
+        <v>589459</v>
       </c>
       <c r="R15" t="n">
-        <v>6931387</v>
+        <v>6931441</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2285,7 +2302,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2295,12 +2312,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125285335</v>
+        <v>125283250</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>58111</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,27 +2355,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2372,10 +2384,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589527</v>
+        <v>589679</v>
       </c>
       <c r="R16" t="n">
-        <v>6931442</v>
+        <v>6931418</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2419,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,12 +2429,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2449,10 +2456,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125285242</v>
+        <v>125283973</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
+        <v>91177</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2461,43 +2468,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589459</v>
+        <v>589587</v>
       </c>
       <c r="R17" t="n">
-        <v>6931441</v>
+        <v>6931481</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2529,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2539,7 +2541,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,22 +2556,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125284424</v>
+        <v>125285367</v>
       </c>
       <c r="B18" t="n">
-        <v>56828</v>
+        <v>105293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2578,43 +2580,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589508</v>
+        <v>589527</v>
       </c>
       <c r="R18" t="n">
-        <v>6931482</v>
+        <v>6931442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2646,7 +2643,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2656,7 +2653,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2671,12 +2668,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2805,7 +2802,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125286793</v>
+        <v>125285335</v>
       </c>
       <c r="B20" t="n">
         <v>57635</v>
@@ -2850,10 +2847,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589614</v>
+        <v>589527</v>
       </c>
       <c r="R20" t="n">
-        <v>6931331</v>
+        <v>6931442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2885,7 +2882,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2895,12 +2892,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2927,10 +2924,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125285600</v>
+        <v>125283192</v>
       </c>
       <c r="B21" t="n">
-        <v>80028</v>
+        <v>56836</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2939,38 +2936,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589438</v>
+        <v>589701</v>
       </c>
       <c r="R21" t="n">
-        <v>6931387</v>
+        <v>6931425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3002,7 +3004,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3012,7 +3014,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3039,10 +3046,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125284607</v>
+        <v>125283801</v>
       </c>
       <c r="B22" t="n">
-        <v>92482</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3051,35 +3058,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3088,10 +3091,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589522</v>
+        <v>589633</v>
       </c>
       <c r="R22" t="n">
-        <v>6931472</v>
+        <v>6931451</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3123,7 +3126,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3133,12 +3136,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,22 +3156,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125284881</v>
+        <v>125284936</v>
       </c>
       <c r="B23" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3177,38 +3180,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589483</v>
+        <v>589486</v>
       </c>
       <c r="R23" t="n">
-        <v>6931476</v>
+        <v>6931494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3240,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3250,7 +3257,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3265,22 +3272,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125286223</v>
+        <v>125283609</v>
       </c>
       <c r="B24" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3293,39 +3300,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589552</v>
+        <v>589655</v>
       </c>
       <c r="R24" t="n">
-        <v>6931425</v>
+        <v>6931459</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3357,7 +3359,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3367,7 +3369,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3394,10 +3396,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125283205</v>
+        <v>125287385</v>
       </c>
       <c r="B25" t="n">
-        <v>97147</v>
+        <v>57632</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3406,25 +3408,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3434,10 +3436,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589702</v>
+        <v>589447</v>
       </c>
       <c r="R25" t="n">
-        <v>6931407</v>
+        <v>6931328</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3469,7 +3471,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3479,7 +3481,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3506,10 +3508,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125283192</v>
+        <v>125284988</v>
       </c>
       <c r="B26" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3518,31 +3520,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3551,10 +3552,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589701</v>
+        <v>589474</v>
       </c>
       <c r="R26" t="n">
-        <v>6931425</v>
+        <v>6931483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3586,7 +3587,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3596,12 +3597,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3628,10 +3624,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125283801</v>
+        <v>125283205</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3640,43 +3636,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589633</v>
+        <v>589702</v>
       </c>
       <c r="R27" t="n">
-        <v>6931451</v>
+        <v>6931407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3708,7 +3699,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3718,12 +3709,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3738,19 +3724,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125285519</v>
+        <v>125285099</v>
       </c>
       <c r="B28" t="n">
         <v>57635</v>
@@ -3795,10 +3781,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589515</v>
+        <v>589466</v>
       </c>
       <c r="R28" t="n">
-        <v>6931442</v>
+        <v>6931475</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3830,7 +3816,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3840,12 +3826,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3860,22 +3846,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125285548</v>
+        <v>125290527</v>
       </c>
       <c r="B29" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3888,27 +3874,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3917,10 +3903,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589543</v>
+        <v>589624</v>
       </c>
       <c r="R29" t="n">
-        <v>6931382</v>
+        <v>6931325</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3952,7 +3938,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3962,7 +3948,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3977,19 +3968,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125286606</v>
+        <v>125286223</v>
       </c>
       <c r="B30" t="n">
         <v>57632</v>
@@ -4034,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589602</v>
+        <v>589552</v>
       </c>
       <c r="R30" t="n">
-        <v>6931356</v>
+        <v>6931425</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4069,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4079,7 +4070,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4106,10 +4097,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125283953</v>
+        <v>125284981</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4122,26 +4113,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4150,10 +4142,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589633</v>
+        <v>589475</v>
       </c>
       <c r="R31" t="n">
-        <v>6931451</v>
+        <v>6931470</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,7 +4177,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4195,7 +4187,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4210,22 +4207,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125284251</v>
+        <v>125283860</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4238,26 +4235,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4266,10 +4264,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>589508</v>
+        <v>589606</v>
       </c>
       <c r="R32" t="n">
-        <v>6931482</v>
+        <v>6931471</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4299,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,7 +4309,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4326,22 +4329,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125285099</v>
+        <v>125285293</v>
       </c>
       <c r="B33" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4354,16 +4357,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4383,10 +4386,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589466</v>
+        <v>589459</v>
       </c>
       <c r="R33" t="n">
-        <v>6931475</v>
+        <v>6931441</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4418,7 +4421,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4428,12 +4431,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4460,10 +4463,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125285293</v>
+        <v>125285548</v>
       </c>
       <c r="B34" t="n">
-        <v>56828</v>
+        <v>57793</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4476,27 +4479,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4505,10 +4508,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589459</v>
+        <v>589543</v>
       </c>
       <c r="R34" t="n">
-        <v>6931441</v>
+        <v>6931382</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4540,7 +4543,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4550,12 +4553,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Fjäder Järpe</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4570,22 +4568,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125291148</v>
+        <v>125284367</v>
       </c>
       <c r="B35" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4598,39 +4596,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589727</v>
+        <v>589508</v>
       </c>
       <c r="R35" t="n">
-        <v>6931355</v>
+        <v>6931482</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4662,7 +4655,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4672,12 +4665,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4704,10 +4697,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125284988</v>
+        <v>125286059</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4720,26 +4713,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4748,10 +4742,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589474</v>
+        <v>589552</v>
       </c>
       <c r="R36" t="n">
-        <v>6931483</v>
+        <v>6931425</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4783,7 +4777,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4793,7 +4787,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,19 +4807,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125286059</v>
+        <v>125286793</v>
       </c>
       <c r="B37" t="n">
         <v>57635</v>
@@ -4865,10 +4864,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589552</v>
+        <v>589614</v>
       </c>
       <c r="R37" t="n">
-        <v>6931425</v>
+        <v>6931331</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4900,7 +4899,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4910,7 +4909,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4942,10 +4941,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125287027</v>
+        <v>125283936</v>
       </c>
       <c r="B38" t="n">
-        <v>97147</v>
+        <v>56836</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4958,34 +4957,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589571</v>
+        <v>589597</v>
       </c>
       <c r="R38" t="n">
-        <v>6931323</v>
+        <v>6931482</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5017,7 +5021,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5027,7 +5031,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5054,10 +5063,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125283515</v>
+        <v>125285776</v>
       </c>
       <c r="B39" t="n">
-        <v>92482</v>
+        <v>91177</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5070,43 +5079,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5964</v>
+        <v>1205</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589701</v>
+        <v>589446</v>
       </c>
       <c r="R39" t="n">
-        <v>6931425</v>
+        <v>6931392</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5148,12 +5148,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5168,22 +5163,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125284804</v>
+        <v>125284881</v>
       </c>
       <c r="B40" t="n">
-        <v>56836</v>
+        <v>91166</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5192,43 +5187,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589522</v>
+        <v>589483</v>
       </c>
       <c r="R40" t="n">
-        <v>6931472</v>
+        <v>6931476</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5260,7 +5250,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5270,7 +5260,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5297,10 +5287,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125283973</v>
+        <v>125283173</v>
       </c>
       <c r="B41" t="n">
-        <v>91177</v>
+        <v>57635</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5309,38 +5299,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589587</v>
+        <v>589711</v>
       </c>
       <c r="R41" t="n">
-        <v>6931481</v>
+        <v>6931414</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5370,19 +5365,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:32</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:32</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5409,7 +5399,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125283173</v>
+        <v>125284432</v>
       </c>
       <c r="B42" t="n">
         <v>57635</v>
@@ -5454,10 +5444,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589711</v>
+        <v>589518</v>
       </c>
       <c r="R42" t="n">
-        <v>6931414</v>
+        <v>6931461</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5487,14 +5477,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5643,10 +5643,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125290551</v>
+        <v>125287027</v>
       </c>
       <c r="B44" t="n">
-        <v>91166</v>
+        <v>97147</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5655,25 +5655,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589606</v>
+        <v>589571</v>
       </c>
       <c r="R44" t="n">
-        <v>6931325</v>
+        <v>6931323</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5743,22 +5743,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125316461</v>
+        <v>125316811</v>
       </c>
       <c r="B45" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,39 +5771,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589678</v>
+        <v>589717</v>
       </c>
       <c r="R45" t="n">
-        <v>6931231</v>
+        <v>6931206</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5835,7 +5830,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5845,12 +5840,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5877,7 +5867,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B46" t="n">
         <v>57635</v>
@@ -5922,10 +5912,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R46" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5957,7 +5947,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5967,7 +5957,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5999,10 +5989,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316739</v>
+        <v>125316757</v>
       </c>
       <c r="B47" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6015,39 +6005,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589713</v>
       </c>
       <c r="R47" t="n">
-        <v>6931235</v>
+        <v>6931246</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6079,7 +6064,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6089,12 +6074,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6121,10 +6101,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316757</v>
+        <v>125316461</v>
       </c>
       <c r="B48" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6137,34 +6117,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589713</v>
+        <v>589678</v>
       </c>
       <c r="R48" t="n">
-        <v>6931246</v>
+        <v>6931231</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6196,7 +6181,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6206,7 +6191,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6233,10 +6223,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125316811</v>
+        <v>125316951</v>
       </c>
       <c r="B49" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6249,34 +6239,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R49" t="n">
-        <v>6931206</v>
+        <v>6931248</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6308,7 +6303,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6318,7 +6313,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -3980,10 +3980,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125286223</v>
+        <v>125284981</v>
       </c>
       <c r="B30" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3996,16 +3996,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589552</v>
+        <v>589475</v>
       </c>
       <c r="R30" t="n">
-        <v>6931425</v>
+        <v>6931470</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4070,7 +4070,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,10 +4102,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125284981</v>
+        <v>125286223</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4113,16 +4118,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4142,10 +4147,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589475</v>
+        <v>589552</v>
       </c>
       <c r="R31" t="n">
-        <v>6931470</v>
+        <v>6931425</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,7 +4182,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4187,12 +4192,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4580,10 +4580,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125284367</v>
+        <v>125285776</v>
       </c>
       <c r="B35" t="n">
-        <v>80028</v>
+        <v>91177</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4592,25 +4592,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4620,10 +4620,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589508</v>
+        <v>589446</v>
       </c>
       <c r="R35" t="n">
-        <v>6931482</v>
+        <v>6931392</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4665,12 +4665,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Enormt mycket lunglav</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4685,22 +4680,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125286059</v>
+        <v>125284367</v>
       </c>
       <c r="B36" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4713,39 +4708,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589552</v>
+        <v>589508</v>
       </c>
       <c r="R36" t="n">
-        <v>6931425</v>
+        <v>6931482</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4777,7 +4767,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4787,12 +4777,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4807,19 +4797,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125286793</v>
+        <v>125286059</v>
       </c>
       <c r="B37" t="n">
         <v>57635</v>
@@ -4864,10 +4854,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589614</v>
+        <v>589552</v>
       </c>
       <c r="R37" t="n">
-        <v>6931331</v>
+        <v>6931425</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4899,7 +4889,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4909,7 +4899,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4941,10 +4931,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125283936</v>
+        <v>125286793</v>
       </c>
       <c r="B38" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4953,31 +4943,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4986,10 +4976,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589597</v>
+        <v>589614</v>
       </c>
       <c r="R38" t="n">
-        <v>6931482</v>
+        <v>6931331</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5021,7 +5011,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5031,12 +5021,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5063,10 +5053,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125285776</v>
+        <v>125283936</v>
       </c>
       <c r="B39" t="n">
-        <v>91177</v>
+        <v>56836</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5079,34 +5069,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589446</v>
+        <v>589597</v>
       </c>
       <c r="R39" t="n">
-        <v>6931392</v>
+        <v>6931482</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5138,7 +5133,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5148,7 +5143,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -2339,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125283250</v>
+        <v>125283973</v>
       </c>
       <c r="B16" t="n">
-        <v>58111</v>
+        <v>91177</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2351,43 +2351,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>1205</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589679</v>
+        <v>589587</v>
       </c>
       <c r="R16" t="n">
-        <v>6931418</v>
+        <v>6931481</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2429,7 +2424,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2456,10 +2451,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125283973</v>
+        <v>125283192</v>
       </c>
       <c r="B17" t="n">
-        <v>91177</v>
+        <v>56836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2472,34 +2467,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1205</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589587</v>
+        <v>589701</v>
       </c>
       <c r="R17" t="n">
-        <v>6931481</v>
+        <v>6931425</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2541,7 +2541,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,22 +2561,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125285367</v>
+        <v>125283250</v>
       </c>
       <c r="B18" t="n">
-        <v>105293</v>
+        <v>58111</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,38 +2585,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>103018</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589527</v>
+        <v>589679</v>
       </c>
       <c r="R18" t="n">
-        <v>6931442</v>
+        <v>6931418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2643,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2653,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2924,10 +2934,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125283192</v>
+        <v>125285367</v>
       </c>
       <c r="B21" t="n">
-        <v>56836</v>
+        <v>105293</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2940,39 +2950,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589701</v>
+        <v>589527</v>
       </c>
       <c r="R21" t="n">
-        <v>6931425</v>
+        <v>6931442</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3004,7 +3009,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3014,12 +3019,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3034,12 +3034,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125283953</v>
+        <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589633</v>
+        <v>589602</v>
       </c>
       <c r="R2" t="n">
-        <v>6931451</v>
+        <v>6931356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125286606</v>
+        <v>125284881</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589602</v>
+        <v>589483</v>
       </c>
       <c r="R3" t="n">
-        <v>6931356</v>
+        <v>6931476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,42 +894,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125284251</v>
+        <v>125284607</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -952,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589508</v>
+        <v>589522</v>
       </c>
       <c r="R4" t="n">
-        <v>6931482</v>
+        <v>6931472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +983,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,27 +1003,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125290551</v>
+        <v>125286321</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,34 +1026,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589606</v>
+        <v>589560</v>
       </c>
       <c r="R5" t="n">
-        <v>6931325</v>
+        <v>6931398</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,27 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125286102</v>
+        <v>125283250</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1152,27 +1143,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1181,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589438</v>
+        <v>589679</v>
       </c>
       <c r="R6" t="n">
-        <v>6931387</v>
+        <v>6931418</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,27 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125283515</v>
+        <v>125284804</v>
       </c>
       <c r="B7" t="n">
-        <v>92482</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,31 +1255,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1307,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589701</v>
+        <v>589522</v>
       </c>
       <c r="R7" t="n">
-        <v>6931425</v>
+        <v>6931472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1352,12 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:13</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,27 +1344,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125285519</v>
+        <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,16 +1367,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1429,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589515</v>
+        <v>589552</v>
       </c>
       <c r="R8" t="n">
-        <v>6931442</v>
+        <v>6931425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,12 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,47 +1468,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125284607</v>
+        <v>125283173</v>
       </c>
       <c r="B9" t="n">
-        <v>92482</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1555,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589522</v>
+        <v>589711</v>
       </c>
       <c r="R9" t="n">
-        <v>6931472</v>
+        <v>6931414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,24 +1541,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>09:59</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,15 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125291148</v>
+        <v>125284988</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,27 +1586,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1677,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589727</v>
+        <v>589474</v>
       </c>
       <c r="R10" t="n">
-        <v>6931355</v>
+        <v>6931483</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,12 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,43 +1686,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125284804</v>
+        <v>125284251</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1799,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589522</v>
+        <v>589508</v>
       </c>
       <c r="R11" t="n">
-        <v>6931472</v>
+        <v>6931482</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1834,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1844,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,27 +1785,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125284424</v>
+        <v>125285335</v>
       </c>
       <c r="B12" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,16 +1808,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1916,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589508</v>
+        <v>589527</v>
       </c>
       <c r="R12" t="n">
-        <v>6931482</v>
+        <v>6931442</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1872,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1961,7 +1882,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1976,27 +1902,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125286321</v>
+        <v>125286793</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,10 +1954,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589560</v>
+        <v>589614</v>
       </c>
       <c r="R13" t="n">
-        <v>6931398</v>
+        <v>6931331</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2068,7 +1989,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2078,7 +1999,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2110,15 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125285600</v>
+        <v>125284981</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,34 +2042,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589438</v>
+        <v>589475</v>
       </c>
       <c r="R14" t="n">
-        <v>6931387</v>
+        <v>6931470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2185,7 +2106,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2195,7 +2116,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,27 +2136,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125285242</v>
+        <v>125284367</v>
       </c>
       <c r="B15" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2238,39 +2159,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589459</v>
+        <v>589508</v>
       </c>
       <c r="R15" t="n">
-        <v>6931441</v>
+        <v>6931482</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2312,7 +2228,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2339,50 +2260,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125283973</v>
+        <v>125286102</v>
       </c>
       <c r="B16" t="n">
-        <v>91177</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589587</v>
+        <v>589438</v>
       </c>
       <c r="R16" t="n">
-        <v>6931481</v>
+        <v>6931387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2424,7 +2345,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,27 +2365,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125283192</v>
+        <v>125285367</v>
       </c>
       <c r="B17" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,39 +2388,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589701</v>
+        <v>589527</v>
       </c>
       <c r="R17" t="n">
-        <v>6931425</v>
+        <v>6931442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2531,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2541,12 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,55 +2472,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125283250</v>
+        <v>125284936</v>
       </c>
       <c r="B18" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103018</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2618,10 +2523,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589679</v>
+        <v>589486</v>
       </c>
       <c r="R18" t="n">
-        <v>6931418</v>
+        <v>6931494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2653,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,27 +2583,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125284312</v>
+        <v>125283609</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,39 +2606,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589522</v>
+        <v>589655</v>
       </c>
       <c r="R19" t="n">
-        <v>6931472</v>
+        <v>6931459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2665,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,12 +2675,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,15 +2702,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125285335</v>
+        <v>125284424</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2828,16 +2713,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2857,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589527</v>
+        <v>589508</v>
       </c>
       <c r="R20" t="n">
-        <v>6931442</v>
+        <v>6931482</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2892,7 +2777,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2902,12 +2787,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2922,59 +2802,59 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125285367</v>
+        <v>125285519</v>
       </c>
       <c r="B21" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589527</v>
+        <v>589515</v>
       </c>
       <c r="R21" t="n">
         <v>6931442</v>
@@ -3009,7 +2889,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3019,7 +2899,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3046,15 +2931,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125283801</v>
+        <v>125283953</v>
       </c>
       <c r="B22" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3062,27 +2942,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3126,7 +3005,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3136,12 +3015,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3168,42 +3042,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125284936</v>
+        <v>125284312</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3212,10 +3082,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589486</v>
+        <v>589522</v>
       </c>
       <c r="R23" t="n">
-        <v>6931494</v>
+        <v>6931472</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3117,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,7 +3127,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3272,27 +3147,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125283609</v>
+        <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3300,21 +3170,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3324,10 +3194,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589655</v>
+        <v>589447</v>
       </c>
       <c r="R24" t="n">
-        <v>6931459</v>
+        <v>6931328</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3359,7 +3229,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3369,7 +3239,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3396,37 +3266,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125287385</v>
+        <v>125287027</v>
       </c>
       <c r="B25" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3436,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589447</v>
+        <v>589571</v>
       </c>
       <c r="R25" t="n">
-        <v>6931328</v>
+        <v>6931323</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3471,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3481,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3508,15 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125284988</v>
+        <v>125290551</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3524,38 +3384,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589474</v>
+        <v>589606</v>
       </c>
       <c r="R26" t="n">
-        <v>6931483</v>
+        <v>6931325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3587,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3597,7 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3624,50 +3480,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125283205</v>
+        <v>125290527</v>
       </c>
       <c r="B27" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589702</v>
+        <v>589624</v>
       </c>
       <c r="R27" t="n">
-        <v>6931407</v>
+        <v>6931325</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3699,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3709,7 +3565,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3724,27 +3585,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125285099</v>
+        <v>125283329</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3781,10 +3637,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589466</v>
+        <v>589665</v>
       </c>
       <c r="R28" t="n">
-        <v>6931475</v>
+        <v>6931444</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3816,7 +3672,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3826,12 +3682,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,67 +3702,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125290527</v>
+        <v>125283205</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589624</v>
+        <v>589702</v>
       </c>
       <c r="R29" t="n">
-        <v>6931325</v>
+        <v>6931407</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3938,7 +3784,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3948,12 +3794,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3968,67 +3809,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125284981</v>
+        <v>125285776</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91231</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589475</v>
+        <v>589446</v>
       </c>
       <c r="R30" t="n">
-        <v>6931470</v>
+        <v>6931392</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4060,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4070,12 +3901,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4102,43 +3928,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125286223</v>
+        <v>125283515</v>
       </c>
       <c r="B31" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92536</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4147,7 +3972,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589552</v>
+        <v>589701</v>
       </c>
       <c r="R31" t="n">
         <v>6931425</v>
@@ -4182,7 +4007,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4192,7 +4017,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4207,12 +4037,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4222,12 +4052,7 @@
         <v>125283860</v>
       </c>
       <c r="B32" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4341,15 +4166,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125285293</v>
+        <v>125284432</v>
       </c>
       <c r="B33" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4357,16 +4177,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4386,10 +4206,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589459</v>
+        <v>589518</v>
       </c>
       <c r="R33" t="n">
-        <v>6931441</v>
+        <v>6931461</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4421,7 +4241,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4431,12 +4251,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Fjäder Järpe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4451,27 +4271,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125285548</v>
+        <v>125283801</v>
       </c>
       <c r="B34" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4479,27 +4294,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4508,10 +4323,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589543</v>
+        <v>589633</v>
       </c>
       <c r="R34" t="n">
-        <v>6931382</v>
+        <v>6931451</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4543,7 +4358,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4553,7 +4368,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4568,62 +4388,62 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125285776</v>
+        <v>125286059</v>
       </c>
       <c r="B35" t="n">
-        <v>91177</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589446</v>
+        <v>589552</v>
       </c>
       <c r="R35" t="n">
-        <v>6931392</v>
+        <v>6931425</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4655,7 +4475,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4665,7 +4485,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4692,15 +4517,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125284367</v>
+        <v>125285548</v>
       </c>
       <c r="B36" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4708,34 +4528,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589508</v>
+        <v>589543</v>
       </c>
       <c r="R36" t="n">
-        <v>6931482</v>
+        <v>6931382</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4767,7 +4592,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4777,12 +4602,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Enormt mycket lunglav</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4797,27 +4617,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125286059</v>
+        <v>125285242</v>
       </c>
       <c r="B37" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4825,16 +4640,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4854,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589552</v>
+        <v>589459</v>
       </c>
       <c r="R37" t="n">
-        <v>6931425</v>
+        <v>6931441</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4889,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4899,12 +4714,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:56</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4919,55 +4729,50 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125286793</v>
+        <v>125283936</v>
       </c>
       <c r="B38" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4976,10 +4781,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589614</v>
+        <v>589597</v>
       </c>
       <c r="R38" t="n">
-        <v>6931331</v>
+        <v>6931482</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5011,7 +4816,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5021,12 +4826,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5053,15 +4858,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125283936</v>
+        <v>125283192</v>
       </c>
       <c r="B39" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5089,7 +4889,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5098,10 +4898,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589597</v>
+        <v>589701</v>
       </c>
       <c r="R39" t="n">
-        <v>6931482</v>
+        <v>6931425</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5133,7 +4933,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5143,12 +4943,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5163,27 +4963,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125284881</v>
+        <v>125291148</v>
       </c>
       <c r="B40" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5191,34 +4986,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589483</v>
+        <v>589727</v>
       </c>
       <c r="R40" t="n">
-        <v>6931476</v>
+        <v>6931355</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5250,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5260,7 +5060,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5275,27 +5080,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125283173</v>
+        <v>125285099</v>
       </c>
       <c r="B41" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5332,10 +5132,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589711</v>
+        <v>589466</v>
       </c>
       <c r="R41" t="n">
-        <v>6931414</v>
+        <v>6931475</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5365,14 +5165,24 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5387,67 +5197,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125284432</v>
+        <v>125283973</v>
       </c>
       <c r="B42" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91231</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589518</v>
+        <v>589587</v>
       </c>
       <c r="R42" t="n">
-        <v>6931461</v>
+        <v>6931481</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5479,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5489,12 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5521,15 +5316,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125283329</v>
+        <v>125285600</v>
       </c>
       <c r="B43" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5537,39 +5327,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589665</v>
+        <v>589438</v>
       </c>
       <c r="R43" t="n">
-        <v>6931444</v>
+        <v>6931387</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5601,7 +5386,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5611,12 +5396,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5631,62 +5411,62 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125287027</v>
+        <v>125285293</v>
       </c>
       <c r="B44" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589571</v>
+        <v>589459</v>
       </c>
       <c r="R44" t="n">
-        <v>6931323</v>
+        <v>6931441</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5718,7 +5498,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5728,7 +5508,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5743,27 +5528,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125316811</v>
+        <v>125316461</v>
       </c>
       <c r="B45" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5771,34 +5551,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>589717</v>
+        <v>589678</v>
       </c>
       <c r="R45" t="n">
-        <v>6931206</v>
+        <v>6931231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5830,7 +5615,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5840,7 +5625,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5867,15 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B46" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5912,10 +5697,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R46" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5947,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5957,7 +5742,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5989,15 +5774,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316757</v>
+        <v>125316739</v>
       </c>
       <c r="B47" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6005,34 +5785,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589713</v>
+        <v>589717</v>
       </c>
       <c r="R47" t="n">
-        <v>6931246</v>
+        <v>6931235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6064,7 +5849,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6074,7 +5859,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6101,15 +5891,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316461</v>
+        <v>125316811</v>
       </c>
       <c r="B48" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6117,39 +5902,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589678</v>
+        <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931231</v>
+        <v>6931206</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6181,7 +5961,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6191,12 +5971,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6223,15 +5998,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125316951</v>
+        <v>125316757</v>
       </c>
       <c r="B49" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6239,39 +6009,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589777</v>
+        <v>589713</v>
       </c>
       <c r="R49" t="n">
-        <v>6931248</v>
+        <v>6931246</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6303,7 +6068,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6313,12 +6078,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -1132,38 +1132,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125283250</v>
+        <v>125284804</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589679</v>
+        <v>589522</v>
       </c>
       <c r="R6" t="n">
-        <v>6931418</v>
+        <v>6931472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125284804</v>
+        <v>125283250</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>58129</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589522</v>
+        <v>589679</v>
       </c>
       <c r="R7" t="n">
-        <v>6931472</v>
+        <v>6931418</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316951</v>
+        <v>125316811</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5668,39 +5668,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R46" t="n">
-        <v>6931248</v>
+        <v>6931206</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5727,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,12 +5737,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5774,7 +5764,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B47" t="n">
         <v>57651</v>
@@ -5814,10 +5804,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R47" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,7 +5839,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5859,7 +5849,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5891,10 +5881,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316811</v>
+        <v>125316739</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,24 +5892,29 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
@@ -5929,7 +5924,7 @@
         <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931206</v>
+        <v>6931235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5961,7 +5956,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5971,7 +5966,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125284881</v>
       </c>
       <c r="B3" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125284607</v>
       </c>
       <c r="B4" t="n">
-        <v>92536</v>
+        <v>92543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,38 +1132,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125284804</v>
+        <v>125283250</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589522</v>
+        <v>589679</v>
       </c>
       <c r="R6" t="n">
-        <v>6931472</v>
+        <v>6931418</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125283250</v>
+        <v>125284804</v>
       </c>
       <c r="B7" t="n">
-        <v>58129</v>
+        <v>56843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589679</v>
+        <v>589522</v>
       </c>
       <c r="R7" t="n">
-        <v>6931418</v>
+        <v>6931472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125286223</v>
+        <v>125283173</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589552</v>
+        <v>589711</v>
       </c>
       <c r="R8" t="n">
-        <v>6931425</v>
+        <v>6931414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,19 +1429,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:59</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125283173</v>
+        <v>125286223</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,16 +1474,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1508,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589711</v>
+        <v>589552</v>
       </c>
       <c r="R9" t="n">
-        <v>6931414</v>
+        <v>6931425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,14 +1536,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2260,38 +2260,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125286102</v>
+        <v>125284936</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2300,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589438</v>
+        <v>589486</v>
       </c>
       <c r="R16" t="n">
-        <v>6931387</v>
+        <v>6931494</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,12 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,45 +2371,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125285367</v>
+        <v>125286102</v>
       </c>
       <c r="B17" t="n">
-        <v>105348</v>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589527</v>
+        <v>589438</v>
       </c>
       <c r="R17" t="n">
-        <v>6931442</v>
+        <v>6931387</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2456,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,61 +2476,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125284936</v>
+        <v>125285367</v>
       </c>
       <c r="B18" t="n">
-        <v>98324</v>
+        <v>105355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589486</v>
+        <v>589527</v>
       </c>
       <c r="R18" t="n">
-        <v>6931494</v>
+        <v>6931442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,12 +2583,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3266,32 +3266,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125287027</v>
+        <v>125290551</v>
       </c>
       <c r="B25" t="n">
-        <v>97202</v>
+        <v>91227</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589571</v>
+        <v>589606</v>
       </c>
       <c r="R25" t="n">
-        <v>6931323</v>
+        <v>6931325</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,22 +3361,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125290551</v>
+        <v>125290527</v>
       </c>
       <c r="B26" t="n">
-        <v>91220</v>
+        <v>57651</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3384,31 +3384,36 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589606</v>
+        <v>589624</v>
       </c>
       <c r="R26" t="n">
         <v>6931325</v>
@@ -3443,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3458,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,50 +3490,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125290527</v>
+        <v>125287027</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589624</v>
+        <v>589571</v>
       </c>
       <c r="R27" t="n">
-        <v>6931325</v>
+        <v>6931323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3555,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,12 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,62 +3585,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283329</v>
+        <v>125283205</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589665</v>
+        <v>589702</v>
       </c>
       <c r="R28" t="n">
-        <v>6931444</v>
+        <v>6931407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,12 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,45 +3704,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125283205</v>
+        <v>125283329</v>
       </c>
       <c r="B29" t="n">
-        <v>97202</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589702</v>
+        <v>589665</v>
       </c>
       <c r="R29" t="n">
-        <v>6931407</v>
+        <v>6931444</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3794,7 +3789,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,7 +3824,7 @@
         <v>125285776</v>
       </c>
       <c r="B30" t="n">
-        <v>91231</v>
+        <v>91238</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>125283515</v>
       </c>
       <c r="B31" t="n">
-        <v>92536</v>
+        <v>92543</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4629,38 +4629,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125285242</v>
+        <v>125283192</v>
       </c>
       <c r="B37" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589459</v>
+        <v>589701</v>
       </c>
       <c r="R37" t="n">
-        <v>6931441</v>
+        <v>6931425</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,7 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4858,38 +4863,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125283192</v>
+        <v>125285242</v>
       </c>
       <c r="B39" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4898,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589701</v>
+        <v>589459</v>
       </c>
       <c r="R39" t="n">
-        <v>6931425</v>
+        <v>6931441</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4933,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,12 +4948,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5092,10 +5092,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125285099</v>
+        <v>125285293</v>
       </c>
       <c r="B41" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5103,16 +5103,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589466</v>
+        <v>589459</v>
       </c>
       <c r="R41" t="n">
-        <v>6931475</v>
+        <v>6931441</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,32 +5209,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125283973</v>
+        <v>125285600</v>
       </c>
       <c r="B42" t="n">
-        <v>91231</v>
+        <v>80070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5244,10 +5244,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589587</v>
+        <v>589438</v>
       </c>
       <c r="R42" t="n">
-        <v>6931481</v>
+        <v>6931387</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5304,44 +5304,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125285600</v>
+        <v>125283973</v>
       </c>
       <c r="B43" t="n">
-        <v>80070</v>
+        <v>91238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5351,10 +5351,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589438</v>
+        <v>589587</v>
       </c>
       <c r="R43" t="n">
-        <v>6931387</v>
+        <v>6931481</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,22 +5411,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125285293</v>
+        <v>125285099</v>
       </c>
       <c r="B44" t="n">
-        <v>56834</v>
+        <v>57651</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5434,16 +5434,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589459</v>
+        <v>589466</v>
       </c>
       <c r="R44" t="n">
-        <v>6931441</v>
+        <v>6931475</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Fjäder Järpe</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5764,7 +5764,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B47" t="n">
         <v>57651</v>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R47" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B48" t="n">
         <v>57651</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R48" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -2260,37 +2260,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125284936</v>
+        <v>125286102</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2299,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589486</v>
+        <v>589438</v>
       </c>
       <c r="R16" t="n">
-        <v>6931494</v>
+        <v>6931387</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2334,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2344,7 +2345,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,50 +2377,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125286102</v>
+        <v>125285367</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>105355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589438</v>
+        <v>589527</v>
       </c>
       <c r="R17" t="n">
-        <v>6931387</v>
+        <v>6931442</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,12 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,57 +2472,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125285367</v>
+        <v>125284936</v>
       </c>
       <c r="B18" t="n">
-        <v>105355</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589527</v>
+        <v>589486</v>
       </c>
       <c r="R18" t="n">
-        <v>6931442</v>
+        <v>6931494</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,12 +2583,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3373,50 +3373,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125290527</v>
+        <v>125287027</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589624</v>
+        <v>589571</v>
       </c>
       <c r="R26" t="n">
-        <v>6931325</v>
+        <v>6931323</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,7 +3443,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,12 +3453,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,57 +3468,62 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125287027</v>
+        <v>125290527</v>
       </c>
       <c r="B27" t="n">
-        <v>97209</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589571</v>
+        <v>589624</v>
       </c>
       <c r="R27" t="n">
-        <v>6931323</v>
+        <v>6931325</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3560,7 +3555,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3565,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,12 +3585,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4629,7 +4629,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125283192</v>
+        <v>125283936</v>
       </c>
       <c r="B37" t="n">
         <v>56843</v>
@@ -4660,7 +4660,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589701</v>
+        <v>589597</v>
       </c>
       <c r="R37" t="n">
-        <v>6931425</v>
+        <v>6931482</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4734,50 +4734,50 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125283936</v>
+        <v>125285242</v>
       </c>
       <c r="B38" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589597</v>
+        <v>589459</v>
       </c>
       <c r="R38" t="n">
-        <v>6931482</v>
+        <v>6931441</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4831,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4851,50 +4846,50 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125285242</v>
+        <v>125283192</v>
       </c>
       <c r="B39" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4903,10 +4898,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589459</v>
+        <v>589701</v>
       </c>
       <c r="R39" t="n">
-        <v>6931441</v>
+        <v>6931425</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4938,7 +4933,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4948,7 +4943,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316811</v>
+        <v>125316739</v>
       </c>
       <c r="B46" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5668,24 +5668,29 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
@@ -5695,7 +5700,7 @@
         <v>589717</v>
       </c>
       <c r="R46" t="n">
-        <v>6931206</v>
+        <v>6931235</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5727,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5737,7 +5742,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,7 +5774,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B47" t="n">
         <v>57651</v>
@@ -5804,10 +5814,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R47" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5839,7 +5849,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5849,7 +5859,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5881,10 +5891,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316951</v>
+        <v>125316811</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5892,39 +5902,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931248</v>
+        <v>6931206</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5956,7 +5961,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5966,12 +5971,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -3597,45 +3597,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283205</v>
+        <v>125283329</v>
       </c>
       <c r="B28" t="n">
-        <v>97209</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589702</v>
+        <v>589665</v>
       </c>
       <c r="R28" t="n">
-        <v>6931407</v>
+        <v>6931444</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,7 +3672,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3682,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,50 +3714,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125283329</v>
+        <v>125283205</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589665</v>
+        <v>589702</v>
       </c>
       <c r="R29" t="n">
-        <v>6931444</v>
+        <v>6931407</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3779,7 +3784,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,12 +3794,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4629,7 +4629,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125283936</v>
+        <v>125283192</v>
       </c>
       <c r="B37" t="n">
         <v>56843</v>
@@ -4660,7 +4660,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589597</v>
+        <v>589701</v>
       </c>
       <c r="R37" t="n">
-        <v>6931482</v>
+        <v>6931425</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4734,12 +4734,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4858,38 +4858,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125283192</v>
+        <v>125291148</v>
       </c>
       <c r="B39" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589701</v>
+        <v>589727</v>
       </c>
       <c r="R39" t="n">
-        <v>6931425</v>
+        <v>6931355</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,38 +4975,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125291148</v>
+        <v>125283936</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589727</v>
+        <v>589597</v>
       </c>
       <c r="R40" t="n">
-        <v>6931355</v>
+        <v>6931482</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5080,12 +5080,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316739</v>
+        <v>125316811</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5668,29 +5668,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
@@ -5700,7 +5695,7 @@
         <v>589717</v>
       </c>
       <c r="R46" t="n">
-        <v>6931235</v>
+        <v>6931206</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5727,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,12 +5737,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5774,7 +5764,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B47" t="n">
         <v>57651</v>
@@ -5814,10 +5804,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R47" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,7 +5839,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5859,7 +5849,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5891,10 +5881,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316811</v>
+        <v>125316951</v>
       </c>
       <c r="B48" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,34 +5892,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R48" t="n">
-        <v>6931206</v>
+        <v>6931248</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5961,7 +5956,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5971,7 +5966,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>125284881</v>
       </c>
       <c r="B3" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>125284607</v>
       </c>
       <c r="B4" t="n">
-        <v>92543</v>
+        <v>92552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,38 +1132,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125283250</v>
+        <v>125284804</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589679</v>
+        <v>589522</v>
       </c>
       <c r="R6" t="n">
-        <v>6931418</v>
+        <v>6931472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,38 +1244,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125284804</v>
+        <v>125283250</v>
       </c>
       <c r="B7" t="n">
-        <v>56843</v>
+        <v>58130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103018</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589522</v>
+        <v>589679</v>
       </c>
       <c r="R7" t="n">
-        <v>6931472</v>
+        <v>6931418</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125283173</v>
+        <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,16 +1367,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589711</v>
+        <v>589552</v>
       </c>
       <c r="R8" t="n">
-        <v>6931414</v>
+        <v>6931425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,14 +1429,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125286223</v>
+        <v>125283173</v>
       </c>
       <c r="B9" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,16 +1479,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1503,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589552</v>
+        <v>589711</v>
       </c>
       <c r="R9" t="n">
-        <v>6931425</v>
+        <v>6931414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,19 +1541,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:59</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,7 +1578,7 @@
         <v>125284988</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>125284251</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>125284367</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2377,45 +2377,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125285367</v>
+        <v>125284936</v>
       </c>
       <c r="B17" t="n">
-        <v>105355</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589527</v>
+        <v>589486</v>
       </c>
       <c r="R17" t="n">
-        <v>6931442</v>
+        <v>6931494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,7 +2451,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2461,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,61 +2476,57 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125284936</v>
+        <v>125285367</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>105358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589486</v>
+        <v>589527</v>
       </c>
       <c r="R18" t="n">
-        <v>6931494</v>
+        <v>6931442</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,22 +2583,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125283609</v>
+        <v>125285519</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,34 +2606,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589655</v>
+        <v>589515</v>
       </c>
       <c r="R19" t="n">
-        <v>6931459</v>
+        <v>6931442</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2665,7 +2670,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2675,7 +2680,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2702,10 +2712,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125284424</v>
+        <v>125283609</v>
       </c>
       <c r="B20" t="n">
-        <v>56834</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,39 +2723,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589508</v>
+        <v>589655</v>
       </c>
       <c r="R20" t="n">
-        <v>6931482</v>
+        <v>6931459</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2777,7 +2782,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2787,7 +2792,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2802,22 +2807,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125285519</v>
+        <v>125284424</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,16 +2830,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2854,10 +2859,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589515</v>
+        <v>589508</v>
       </c>
       <c r="R21" t="n">
-        <v>6931442</v>
+        <v>6931482</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,7 +2894,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2899,12 +2904,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:36</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,12 +2919,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2934,7 +2934,7 @@
         <v>125283953</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125290551</v>
+        <v>125290527</v>
       </c>
       <c r="B25" t="n">
-        <v>91227</v>
+        <v>57651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3277,31 +3277,36 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589606</v>
+        <v>589624</v>
       </c>
       <c r="R25" t="n">
         <v>6931325</v>
@@ -3336,7 +3341,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3351,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,32 +3383,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125287027</v>
+        <v>125290551</v>
       </c>
       <c r="B26" t="n">
-        <v>97209</v>
+        <v>91228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3408,10 +3418,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589571</v>
+        <v>589606</v>
       </c>
       <c r="R26" t="n">
-        <v>6931323</v>
+        <v>6931325</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3443,7 +3453,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3453,7 +3463,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3468,62 +3478,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125290527</v>
+        <v>125287027</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589624</v>
+        <v>589571</v>
       </c>
       <c r="R27" t="n">
-        <v>6931325</v>
+        <v>6931323</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3555,7 +3560,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3565,12 +3570,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3585,62 +3585,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283329</v>
+        <v>125283205</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589665</v>
+        <v>589702</v>
       </c>
       <c r="R28" t="n">
-        <v>6931444</v>
+        <v>6931407</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,7 +3667,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,12 +3677,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,45 +3704,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125283205</v>
+        <v>125283329</v>
       </c>
       <c r="B29" t="n">
-        <v>97209</v>
+        <v>57651</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589702</v>
+        <v>589665</v>
       </c>
       <c r="R29" t="n">
-        <v>6931407</v>
+        <v>6931444</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3784,7 +3779,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3794,7 +3789,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,7 +3824,7 @@
         <v>125285776</v>
       </c>
       <c r="B30" t="n">
-        <v>91238</v>
+        <v>91239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>125283515</v>
       </c>
       <c r="B31" t="n">
-        <v>92543</v>
+        <v>92552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4629,38 +4629,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125283192</v>
+        <v>125291148</v>
       </c>
       <c r="B37" t="n">
-        <v>56843</v>
+        <v>57651</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4669,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589701</v>
+        <v>589727</v>
       </c>
       <c r="R37" t="n">
-        <v>6931425</v>
+        <v>6931355</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4714,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4746,38 +4746,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125285242</v>
+        <v>125283936</v>
       </c>
       <c r="B38" t="n">
-        <v>57648</v>
+        <v>56843</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589459</v>
+        <v>589597</v>
       </c>
       <c r="R38" t="n">
-        <v>6931441</v>
+        <v>6931482</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,7 +4831,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4846,50 +4851,50 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125291148</v>
+        <v>125283192</v>
       </c>
       <c r="B39" t="n">
-        <v>57651</v>
+        <v>56843</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4898,10 +4903,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589727</v>
+        <v>589701</v>
       </c>
       <c r="R39" t="n">
-        <v>6931355</v>
+        <v>6931425</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4933,7 +4938,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4943,12 +4948,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4975,38 +4980,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125283936</v>
+        <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>56843</v>
+        <v>57648</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589597</v>
+        <v>589459</v>
       </c>
       <c r="R40" t="n">
-        <v>6931482</v>
+        <v>6931441</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5050,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5060,12 +5065,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5080,22 +5080,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125285293</v>
+        <v>125285600</v>
       </c>
       <c r="B41" t="n">
-        <v>56834</v>
+        <v>80071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5103,39 +5103,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589459</v>
+        <v>589438</v>
       </c>
       <c r="R41" t="n">
-        <v>6931441</v>
+        <v>6931387</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5177,12 +5172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Fjäder Järpe</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,32 +5199,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125285600</v>
+        <v>125283973</v>
       </c>
       <c r="B42" t="n">
-        <v>80070</v>
+        <v>91239</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5244,10 +5234,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589438</v>
+        <v>589587</v>
       </c>
       <c r="R42" t="n">
-        <v>6931387</v>
+        <v>6931481</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5279,7 +5269,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5289,7 +5279,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5304,57 +5294,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125283973</v>
+        <v>125285099</v>
       </c>
       <c r="B43" t="n">
-        <v>91238</v>
+        <v>57651</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589587</v>
+        <v>589466</v>
       </c>
       <c r="R43" t="n">
-        <v>6931481</v>
+        <v>6931475</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5386,7 +5381,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5396,7 +5391,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5411,22 +5411,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125285099</v>
+        <v>125285293</v>
       </c>
       <c r="B44" t="n">
-        <v>57651</v>
+        <v>56834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5434,16 +5434,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589466</v>
+        <v>589459</v>
       </c>
       <c r="R44" t="n">
-        <v>6931475</v>
+        <v>6931441</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5508,12 +5508,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5660,7 +5660,7 @@
         <v>125316811</v>
       </c>
       <c r="B46" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B47" t="n">
         <v>57651</v>
@@ -5804,10 +5804,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R47" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B48" t="n">
         <v>57651</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -6001,7 +6001,7 @@
         <v>125316757</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -1575,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125284988</v>
+        <v>125285335</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,26 +1586,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1614,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589474</v>
+        <v>589527</v>
       </c>
       <c r="R10" t="n">
-        <v>6931483</v>
+        <v>6931442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,22 +1680,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125284251</v>
+        <v>125286793</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,26 +1703,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1725,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589508</v>
+        <v>589614</v>
       </c>
       <c r="R11" t="n">
-        <v>6931482</v>
+        <v>6931331</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1770,7 +1777,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,19 +1797,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125285335</v>
+        <v>125284981</v>
       </c>
       <c r="B12" t="n">
         <v>57651</v>
@@ -1837,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589527</v>
+        <v>589475</v>
       </c>
       <c r="R12" t="n">
-        <v>6931442</v>
+        <v>6931470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,7 +1884,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1882,12 +1894,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125286793</v>
+        <v>125284988</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,27 +1937,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1954,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589614</v>
+        <v>589474</v>
       </c>
       <c r="R13" t="n">
-        <v>6931331</v>
+        <v>6931483</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1999,12 +2010,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,22 +2025,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125284981</v>
+        <v>125284251</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,27 +2048,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2071,10 +2076,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589475</v>
+        <v>589508</v>
       </c>
       <c r="R14" t="n">
-        <v>6931470</v>
+        <v>6931482</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2106,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2116,12 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,12 +2136,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3597,45 +3597,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283205</v>
+        <v>125283329</v>
       </c>
       <c r="B28" t="n">
-        <v>97212</v>
+        <v>57651</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589702</v>
+        <v>589665</v>
       </c>
       <c r="R28" t="n">
-        <v>6931407</v>
+        <v>6931444</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3667,7 +3672,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3677,7 +3682,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,50 +3714,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125283329</v>
+        <v>125283205</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>97212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589665</v>
+        <v>589702</v>
       </c>
       <c r="R29" t="n">
-        <v>6931444</v>
+        <v>6931407</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3779,7 +3784,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3789,12 +3794,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5092,32 +5092,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125285600</v>
+        <v>125283973</v>
       </c>
       <c r="B41" t="n">
-        <v>80071</v>
+        <v>91239</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5127,10 +5127,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589438</v>
+        <v>589587</v>
       </c>
       <c r="R41" t="n">
-        <v>6931387</v>
+        <v>6931481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,7 +5162,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5187,44 +5187,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125283973</v>
+        <v>125285600</v>
       </c>
       <c r="B42" t="n">
-        <v>91239</v>
+        <v>80071</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589587</v>
+        <v>589438</v>
       </c>
       <c r="R42" t="n">
-        <v>6931481</v>
+        <v>6931387</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5294,12 +5294,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -5657,10 +5657,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316811</v>
+        <v>125316951</v>
       </c>
       <c r="B46" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5668,34 +5668,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R46" t="n">
-        <v>6931206</v>
+        <v>6931248</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5727,7 +5732,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5737,7 +5742,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5764,7 +5774,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B47" t="n">
         <v>57651</v>
@@ -5804,10 +5814,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R47" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5839,7 +5849,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5849,7 +5859,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5881,10 +5891,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316739</v>
+        <v>125316811</v>
       </c>
       <c r="B48" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5892,29 +5902,24 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
@@ -5924,7 +5929,7 @@
         <v>589717</v>
       </c>
       <c r="R48" t="n">
-        <v>6931235</v>
+        <v>6931206</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5956,7 +5961,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5966,12 +5971,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6001,7 +6001,7 @@
         <v>125316757</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125286606</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>125286223</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>125287385</v>
       </c>
       <c r="B24" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>125285242</v>
       </c>
       <c r="B40" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>125286321</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>125283173</v>
       </c>
       <c r="B9" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125285335</v>
       </c>
       <c r="B10" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>125286793</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>125284981</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>125286102</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>125285519</v>
       </c>
       <c r="B19" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125284312</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>125290527</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>125283329</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>125283860</v>
       </c>
       <c r="B32" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>125284432</v>
       </c>
       <c r="B33" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>125283801</v>
       </c>
       <c r="B34" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>125286059</v>
       </c>
       <c r="B35" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>125291148</v>
       </c>
       <c r="B37" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>125285099</v>
       </c>
       <c r="B43" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>125316461</v>
       </c>
       <c r="B45" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>125316951</v>
       </c>
       <c r="B46" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>125316739</v>
       </c>
       <c r="B47" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -1018,7 +1018,7 @@
         <v>125286321</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>125283173</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>125285335</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>125286793</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>125284981</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>125286102</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>125285519</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>125284312</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>125290527</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>125283329</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>125283860</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>125284432</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>125283801</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>125286059</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>125291148</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>125285099</v>
       </c>
       <c r="B43" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>125316461</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>125316951</v>
       </c>
       <c r="B46" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>125316739</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6103,1303 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132783585</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>185</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>589488</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6931431</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132783581</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>589470</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6931399</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132783577</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>589707</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6931221</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132783576</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>589637</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6931188</v>
+      </c>
+      <c r="S53" t="n">
+        <v>7</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132783580</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>589467</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6931395</v>
+      </c>
+      <c r="S54" t="n">
+        <v>11</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132783569</v>
+      </c>
+      <c r="B55" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>589503</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6931444</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132783579</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>589469</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6931399</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132783582</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>589464</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6931404</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132783583</v>
+      </c>
+      <c r="B58" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>589487</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6931429</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132783586</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80305</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>392</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>589503</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6931410</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132783578</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>589520</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6931361</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132783575</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>589691</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6931244</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6426,10 +6426,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132783576</v>
+        <v>132783580</v>
       </c>
       <c r="B53" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,45 +6437,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589637</v>
+        <v>589467</v>
       </c>
       <c r="R53" t="n">
-        <v>6931188</v>
+        <v>6931395</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6504,7 +6496,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6514,12 +6506,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6546,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783580</v>
+        <v>132783576</v>
       </c>
       <c r="B54" t="n">
-        <v>80432</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6557,37 +6544,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589467</v>
+        <v>589637</v>
       </c>
       <c r="R54" t="n">
-        <v>6931395</v>
+        <v>6931188</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6616,7 +6611,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6626,7 +6621,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6105,10 +6105,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132783585</v>
+        <v>132783581</v>
       </c>
       <c r="B50" t="n">
-        <v>79359</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589488</v>
+        <v>589470</v>
       </c>
       <c r="R50" t="n">
-        <v>6931431</v>
+        <v>6931399</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6212,10 +6212,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132783581</v>
+        <v>132783585</v>
       </c>
       <c r="B51" t="n">
-        <v>80432</v>
+        <v>79359</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589470</v>
+        <v>589488</v>
       </c>
       <c r="R51" t="n">
-        <v>6931399</v>
+        <v>6931431</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6105,10 +6105,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132783581</v>
+        <v>132783585</v>
       </c>
       <c r="B50" t="n">
-        <v>80432</v>
+        <v>79360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589470</v>
+        <v>589488</v>
       </c>
       <c r="R50" t="n">
-        <v>6931399</v>
+        <v>6931431</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6212,10 +6212,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132783585</v>
+        <v>132783581</v>
       </c>
       <c r="B51" t="n">
-        <v>79359</v>
+        <v>80433</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589488</v>
+        <v>589470</v>
       </c>
       <c r="R51" t="n">
-        <v>6931431</v>
+        <v>6931399</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6322,7 +6322,7 @@
         <v>132783577</v>
       </c>
       <c r="B52" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6426,10 +6426,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132783580</v>
+        <v>132783569</v>
       </c>
       <c r="B53" t="n">
-        <v>80432</v>
+        <v>91910</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589467</v>
+        <v>589503</v>
       </c>
       <c r="R53" t="n">
-        <v>6931395</v>
+        <v>6931444</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6491,22 +6491,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783576</v>
+        <v>132783580</v>
       </c>
       <c r="B54" t="n">
-        <v>57953</v>
+        <v>80433</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,45 +6544,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589637</v>
+        <v>589467</v>
       </c>
       <c r="R54" t="n">
-        <v>6931188</v>
+        <v>6931395</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6611,7 +6603,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6621,12 +6613,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783569</v>
+        <v>132783576</v>
       </c>
       <c r="B55" t="n">
-        <v>91909</v>
+        <v>57954</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6664,37 +6651,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589503</v>
+        <v>589637</v>
       </c>
       <c r="R55" t="n">
-        <v>6931444</v>
+        <v>6931188</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,22 +6713,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6763,7 +6763,7 @@
         <v>132783579</v>
       </c>
       <c r="B56" t="n">
-        <v>80461</v>
+        <v>80462</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>132783582</v>
       </c>
       <c r="B57" t="n">
-        <v>80392</v>
+        <v>80393</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>132783583</v>
       </c>
       <c r="B58" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>132783586</v>
       </c>
       <c r="B59" t="n">
-        <v>80305</v>
+        <v>80306</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,7 +7191,7 @@
         <v>132783578</v>
       </c>
       <c r="B60" t="n">
-        <v>80336</v>
+        <v>80337</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>132783575</v>
       </c>
       <c r="B61" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6426,10 +6426,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132783580</v>
+        <v>132783569</v>
       </c>
       <c r="B53" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589467</v>
+        <v>589503</v>
       </c>
       <c r="R53" t="n">
-        <v>6931395</v>
+        <v>6931444</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6491,22 +6491,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783569</v>
+        <v>132783580</v>
       </c>
       <c r="B54" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,21 +6544,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6568,13 +6568,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589503</v>
+        <v>589467</v>
       </c>
       <c r="R54" t="n">
-        <v>6931444</v>
+        <v>6931395</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6598,22 +6598,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6426,10 +6426,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132783569</v>
+        <v>132783580</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589503</v>
+        <v>589467</v>
       </c>
       <c r="R53" t="n">
-        <v>6931444</v>
+        <v>6931395</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6491,22 +6491,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783580</v>
+        <v>132783576</v>
       </c>
       <c r="B54" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,37 +6544,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589467</v>
+        <v>589637</v>
       </c>
       <c r="R54" t="n">
-        <v>6931395</v>
+        <v>6931188</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6603,7 +6611,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6613,7 +6621,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783576</v>
+        <v>132783569</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>91918</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6651,45 +6664,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589637</v>
+        <v>589503</v>
       </c>
       <c r="R55" t="n">
-        <v>6931188</v>
+        <v>6931444</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6713,27 +6718,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6974,32 +6974,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132783586</v>
+        <v>132783583</v>
       </c>
       <c r="B58" t="n">
-        <v>80311</v>
+        <v>91918</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>392</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589503</v>
+        <v>589487</v>
       </c>
       <c r="R58" t="n">
-        <v>6931410</v>
+        <v>6931429</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7081,32 +7081,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132783583</v>
+        <v>132783586</v>
       </c>
       <c r="B59" t="n">
-        <v>91918</v>
+        <v>80311</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589487</v>
+        <v>589503</v>
       </c>
       <c r="R59" t="n">
-        <v>6931429</v>
+        <v>6931410</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6426,10 +6426,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132783580</v>
+        <v>132783569</v>
       </c>
       <c r="B53" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6437,21 +6437,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6461,13 +6461,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589467</v>
+        <v>589503</v>
       </c>
       <c r="R53" t="n">
-        <v>6931395</v>
+        <v>6931444</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6491,22 +6491,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6653,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783569</v>
+        <v>132783580</v>
       </c>
       <c r="B55" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6664,21 +6664,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6688,13 +6688,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589503</v>
+        <v>589467</v>
       </c>
       <c r="R55" t="n">
-        <v>6931444</v>
+        <v>6931395</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,22 +6718,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6105,10 +6105,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132783585</v>
+        <v>132783581</v>
       </c>
       <c r="B50" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589488</v>
+        <v>589470</v>
       </c>
       <c r="R50" t="n">
-        <v>6931431</v>
+        <v>6931399</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6212,10 +6212,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132783581</v>
+        <v>132783585</v>
       </c>
       <c r="B51" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589470</v>
+        <v>589488</v>
       </c>
       <c r="R51" t="n">
-        <v>6931399</v>
+        <v>6931431</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783576</v>
+        <v>132783580</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,45 +6544,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589637</v>
+        <v>589467</v>
       </c>
       <c r="R54" t="n">
-        <v>6931188</v>
+        <v>6931395</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6611,7 +6603,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6621,12 +6613,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783580</v>
+        <v>132783576</v>
       </c>
       <c r="B55" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6664,37 +6651,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589467</v>
+        <v>589637</v>
       </c>
       <c r="R55" t="n">
-        <v>6931395</v>
+        <v>6931188</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6723,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6733,7 +6728,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6105,10 +6105,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132783581</v>
+        <v>132783585</v>
       </c>
       <c r="B50" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589470</v>
+        <v>589488</v>
       </c>
       <c r="R50" t="n">
-        <v>6931399</v>
+        <v>6931431</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6212,10 +6212,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132783585</v>
+        <v>132783581</v>
       </c>
       <c r="B51" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589488</v>
+        <v>589470</v>
       </c>
       <c r="R51" t="n">
-        <v>6931431</v>
+        <v>6931399</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783580</v>
+        <v>132783576</v>
       </c>
       <c r="B54" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,37 +6544,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589467</v>
+        <v>589637</v>
       </c>
       <c r="R54" t="n">
-        <v>6931395</v>
+        <v>6931188</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6603,7 +6611,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6613,7 +6621,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783576</v>
+        <v>132783580</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6651,45 +6664,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589637</v>
+        <v>589467</v>
       </c>
       <c r="R55" t="n">
-        <v>6931188</v>
+        <v>6931395</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6723,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,12 +6733,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783576</v>
+        <v>132783580</v>
       </c>
       <c r="B54" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,45 +6544,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589637</v>
+        <v>589467</v>
       </c>
       <c r="R54" t="n">
-        <v>6931188</v>
+        <v>6931395</v>
       </c>
       <c r="S54" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6611,7 +6603,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6621,12 +6613,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6640,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783580</v>
+        <v>132783576</v>
       </c>
       <c r="B55" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6664,37 +6651,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589467</v>
+        <v>589637</v>
       </c>
       <c r="R55" t="n">
-        <v>6931395</v>
+        <v>6931188</v>
       </c>
       <c r="S55" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6723,7 +6718,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6733,7 +6728,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -6105,10 +6105,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132783585</v>
+        <v>132783581</v>
       </c>
       <c r="B50" t="n">
-        <v>79365</v>
+        <v>80438</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6116,21 +6116,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589488</v>
+        <v>589470</v>
       </c>
       <c r="R50" t="n">
-        <v>6931431</v>
+        <v>6931399</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6212,10 +6212,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132783581</v>
+        <v>132783585</v>
       </c>
       <c r="B51" t="n">
-        <v>80438</v>
+        <v>79365</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6223,21 +6223,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589470</v>
+        <v>589488</v>
       </c>
       <c r="R51" t="n">
-        <v>6931399</v>
+        <v>6931431</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783580</v>
+        <v>132783576</v>
       </c>
       <c r="B54" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6544,37 +6544,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589467</v>
+        <v>589637</v>
       </c>
       <c r="R54" t="n">
-        <v>6931395</v>
+        <v>6931188</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6603,7 +6611,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6613,7 +6621,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783576</v>
+        <v>132783580</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6651,45 +6664,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589637</v>
+        <v>589467</v>
       </c>
       <c r="R55" t="n">
-        <v>6931188</v>
+        <v>6931395</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6718,7 +6723,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6728,12 +6733,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125286606</v>
+        <v>132783585</v>
       </c>
       <c r="B2" t="n">
-        <v>57681</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589602</v>
+        <v>589488</v>
       </c>
       <c r="R2" t="n">
-        <v>6931356</v>
+        <v>6931431</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125284881</v>
+        <v>132783586</v>
       </c>
       <c r="B3" t="n">
-        <v>91228</v>
+        <v>80351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589483</v>
+        <v>589503</v>
       </c>
       <c r="R3" t="n">
-        <v>6931476</v>
+        <v>6931410</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125284607</v>
+        <v>125284881</v>
       </c>
       <c r="B4" t="n">
-        <v>92552</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589522</v>
+        <v>589483</v>
       </c>
       <c r="R4" t="n">
-        <v>6931472</v>
+        <v>6931476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125286321</v>
+        <v>125290551</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589560</v>
+        <v>589606</v>
       </c>
       <c r="R5" t="n">
-        <v>6931398</v>
+        <v>6931325</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,65 +1091,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125284804</v>
+        <v>132783569</v>
       </c>
       <c r="B6" t="n">
-        <v>56843</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589522</v>
+        <v>589503</v>
       </c>
       <c r="R6" t="n">
-        <v>6931472</v>
+        <v>6931444</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125283250</v>
+        <v>132783583</v>
       </c>
       <c r="B7" t="n">
-        <v>58130</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,42 +1221,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589679</v>
+        <v>589487</v>
       </c>
       <c r="R7" t="n">
-        <v>6931418</v>
+        <v>6931429</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,50 +1317,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125286223</v>
+        <v>125283973</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>91920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1205</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589552</v>
+        <v>589587</v>
       </c>
       <c r="R8" t="n">
-        <v>6931425</v>
+        <v>6931481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,50 +1424,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125283173</v>
+        <v>125285776</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>91920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589711</v>
+        <v>589446</v>
       </c>
       <c r="R9" t="n">
-        <v>6931414</v>
+        <v>6931392</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,14 +1492,19 @@
           <t>2025-05-21</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125285335</v>
+        <v>125283515</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>93233</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,27 +1542,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589527</v>
+        <v>589701</v>
       </c>
       <c r="R10" t="n">
-        <v>6931442</v>
+        <v>6931425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1620,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,22 +1640,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125286793</v>
+        <v>125284607</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,27 +1663,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5964</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1732,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589614</v>
+        <v>589522</v>
       </c>
       <c r="R11" t="n">
-        <v>6931331</v>
+        <v>6931472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,12 +1741,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar. Grop i mitten. Fjäll på undersidan.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,50 +1773,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125284981</v>
+        <v>125283609</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589475</v>
+        <v>589655</v>
       </c>
       <c r="R12" t="n">
-        <v>6931470</v>
+        <v>6931459</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1843,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,12 +1853,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,14 +1880,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125284988</v>
+        <v>125283953</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1965,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589474</v>
+        <v>589633</v>
       </c>
       <c r="R13" t="n">
-        <v>6931483</v>
+        <v>6931451</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +1954,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,7 +1964,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,11 +1994,11 @@
         <v>125284251</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2148,45 +2102,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125284367</v>
+        <v>125284988</v>
       </c>
       <c r="B15" t="n">
-        <v>80071</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589508</v>
+        <v>589474</v>
       </c>
       <c r="R15" t="n">
-        <v>6931482</v>
+        <v>6931483</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2176,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,12 +2186,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Enormt mycket lunglav</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,50 +2213,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125286102</v>
+        <v>125316757</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589438</v>
+        <v>589713</v>
       </c>
       <c r="R16" t="n">
-        <v>6931387</v>
+        <v>6931246</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,27 +2278,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre spår av tretåig hackspett på Tall</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,22 +2308,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125284936</v>
+        <v>132783575</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2388,41 +2331,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589486</v>
+        <v>589691</v>
       </c>
       <c r="R17" t="n">
-        <v>6931494</v>
+        <v>6931244</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2446,22 +2385,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2476,22 +2415,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125285367</v>
+        <v>132783578</v>
       </c>
       <c r="B18" t="n">
-        <v>105358</v>
+        <v>80382</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,21 +2438,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2523,13 +2462,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>589527</v>
+        <v>589520</v>
       </c>
       <c r="R18" t="n">
-        <v>6931442</v>
+        <v>6931361</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2553,22 +2492,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,10 +2534,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125285519</v>
+        <v>125284367</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,39 +2545,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>589515</v>
+        <v>589508</v>
       </c>
       <c r="R19" t="n">
-        <v>6931442</v>
+        <v>6931482</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2670,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2680,12 +2614,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Enormt mycket lunglav</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2700,22 +2634,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125283609</v>
+        <v>125285600</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2723,21 +2657,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2747,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>589655</v>
+        <v>589438</v>
       </c>
       <c r="R20" t="n">
-        <v>6931459</v>
+        <v>6931387</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2782,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2792,7 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,22 +2741,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125284424</v>
+        <v>125316811</v>
       </c>
       <c r="B21" t="n">
-        <v>56834</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2830,39 +2764,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>589508</v>
+        <v>589717</v>
       </c>
       <c r="R21" t="n">
-        <v>6931482</v>
+        <v>6931206</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2889,22 +2818,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,22 +2848,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125283953</v>
+        <v>132783580</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2942,41 +2871,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>589633</v>
+        <v>589467</v>
       </c>
       <c r="R22" t="n">
-        <v>6931451</v>
+        <v>6931395</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,22 +2925,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,22 +2955,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125284312</v>
+        <v>132783581</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3053,42 +2978,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>589522</v>
+        <v>589470</v>
       </c>
       <c r="R23" t="n">
-        <v>6931472</v>
+        <v>6931399</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3112,27 +3032,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3159,32 +3074,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125287385</v>
+        <v>132783579</v>
       </c>
       <c r="B24" t="n">
-        <v>57681</v>
+        <v>80493</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3194,13 +3109,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>589447</v>
+        <v>589469</v>
       </c>
       <c r="R24" t="n">
-        <v>6931328</v>
+        <v>6931399</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3224,22 +3139,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,27 +3181,27 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125290527</v>
+        <v>125285242</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3306,10 +3221,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>589624</v>
+        <v>589459</v>
       </c>
       <c r="R25" t="n">
-        <v>6931325</v>
+        <v>6931441</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3341,7 +3256,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3351,12 +3266,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3383,45 +3293,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125290551</v>
+        <v>125286223</v>
       </c>
       <c r="B26" t="n">
-        <v>91228</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>589606</v>
+        <v>589552</v>
       </c>
       <c r="R26" t="n">
-        <v>6931325</v>
+        <v>6931425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3453,7 +3368,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3463,7 +3378,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,22 +3393,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125287027</v>
+        <v>125286606</v>
       </c>
       <c r="B27" t="n">
-        <v>97212</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3501,34 +3416,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>589571</v>
+        <v>589602</v>
       </c>
       <c r="R27" t="n">
-        <v>6931323</v>
+        <v>6931356</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3560,7 +3480,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3490,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,27 +3517,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125283329</v>
+        <v>125287385</v>
       </c>
       <c r="B28" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3626,21 +3546,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>589665</v>
+        <v>589447</v>
       </c>
       <c r="R28" t="n">
-        <v>6931444</v>
+        <v>6931328</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3672,7 +3587,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,12 +3597,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,45 +3624,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125283205</v>
+        <v>125283173</v>
       </c>
       <c r="B29" t="n">
-        <v>97212</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>589702</v>
+        <v>589711</v>
       </c>
       <c r="R29" t="n">
-        <v>6931407</v>
+        <v>6931414</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3782,19 +3697,14 @@
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-21</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3821,45 +3731,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125285776</v>
+        <v>125283329</v>
       </c>
       <c r="B30" t="n">
-        <v>91239</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>589446</v>
+        <v>589665</v>
       </c>
       <c r="R30" t="n">
-        <v>6931392</v>
+        <v>6931444</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3891,7 +3806,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,7 +3816,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,42 +3848,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125283515</v>
+        <v>125283801</v>
       </c>
       <c r="B31" t="n">
-        <v>92552</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3972,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>589701</v>
+        <v>589633</v>
       </c>
       <c r="R31" t="n">
-        <v>6931425</v>
+        <v>6931451</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4007,7 +3923,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4017,12 +3933,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4052,7 +3968,7 @@
         <v>125283860</v>
       </c>
       <c r="B32" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4166,10 +4082,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125284432</v>
+        <v>125284312</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4206,10 +4122,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>589518</v>
+        <v>589522</v>
       </c>
       <c r="R33" t="n">
-        <v>6931461</v>
+        <v>6931472</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4241,7 +4157,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4251,7 +4167,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4283,10 +4199,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125283801</v>
+        <v>125284432</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4323,10 +4239,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>589633</v>
+        <v>589518</v>
       </c>
       <c r="R34" t="n">
-        <v>6931451</v>
+        <v>6931461</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4358,7 +4274,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4368,12 +4284,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ett mindre ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,22 +4304,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125286059</v>
+        <v>125284981</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4440,10 +4356,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>589552</v>
+        <v>589475</v>
       </c>
       <c r="R35" t="n">
-        <v>6931425</v>
+        <v>6931470</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4475,7 +4391,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4485,12 +4401,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Syns lite dåligt på bilderna men det har runnit sav/kåda och med kikaren ser man tydliga ringhack.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4517,10 +4433,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125285548</v>
+        <v>125285099</v>
       </c>
       <c r="B36" t="n">
-        <v>57811</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4528,27 +4444,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4557,10 +4473,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>589543</v>
+        <v>589466</v>
       </c>
       <c r="R36" t="n">
-        <v>6931382</v>
+        <v>6931475</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4592,7 +4508,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4602,7 +4518,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4617,22 +4538,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125291148</v>
+        <v>125285335</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4669,10 +4590,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>589727</v>
+        <v>589527</v>
       </c>
       <c r="R37" t="n">
-        <v>6931355</v>
+        <v>6931442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4704,7 +4625,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4714,12 +4635,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4734,50 +4655,50 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125283936</v>
+        <v>125285519</v>
       </c>
       <c r="B38" t="n">
-        <v>56843</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4786,10 +4707,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>589597</v>
+        <v>589515</v>
       </c>
       <c r="R38" t="n">
-        <v>6931482</v>
+        <v>6931442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4821,7 +4742,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4831,12 +4752,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Uppflog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4863,38 +4784,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125283192</v>
+        <v>125286059</v>
       </c>
       <c r="B39" t="n">
-        <v>56843</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4903,7 +4824,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>589701</v>
+        <v>589552</v>
       </c>
       <c r="R39" t="n">
         <v>6931425</v>
@@ -4938,7 +4859,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4948,12 +4869,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Misstänkt natt träd ( tjäder ).</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4968,22 +4889,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125285242</v>
+        <v>125286102</v>
       </c>
       <c r="B40" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4991,16 +4912,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5020,10 +4941,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>589459</v>
+        <v>589438</v>
       </c>
       <c r="R40" t="n">
-        <v>6931441</v>
+        <v>6931387</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5055,7 +4976,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +4986,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre spår av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,45 +5018,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125283973</v>
+        <v>125286321</v>
       </c>
       <c r="B41" t="n">
-        <v>91239</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1205</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>589587</v>
+        <v>589560</v>
       </c>
       <c r="R41" t="n">
-        <v>6931481</v>
+        <v>6931398</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5162,7 +5093,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5172,7 +5103,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5199,10 +5135,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125285600</v>
+        <v>125286793</v>
       </c>
       <c r="B42" t="n">
-        <v>80071</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5210,34 +5146,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>589438</v>
+        <v>589614</v>
       </c>
       <c r="R42" t="n">
-        <v>6931387</v>
+        <v>6931331</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5269,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5279,7 +5220,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5294,22 +5240,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125285099</v>
+        <v>125290527</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5346,10 +5292,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>589466</v>
+        <v>589624</v>
       </c>
       <c r="R43" t="n">
-        <v>6931475</v>
+        <v>6931325</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5381,7 +5327,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5391,12 +5337,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färskt )</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5423,10 +5369,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125285293</v>
+        <v>125291148</v>
       </c>
       <c r="B44" t="n">
-        <v>56834</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5434,16 +5380,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5463,10 +5409,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>589459</v>
+        <v>589727</v>
       </c>
       <c r="R44" t="n">
-        <v>6931441</v>
+        <v>6931355</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5498,7 +5444,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5508,12 +5454,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Fjäder Järpe</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5543,7 +5489,7 @@
         <v>125316461</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5657,10 +5603,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125316951</v>
+        <v>125316739</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5697,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>589777</v>
+        <v>589717</v>
       </c>
       <c r="R46" t="n">
-        <v>6931248</v>
+        <v>6931235</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5732,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5742,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -5774,10 +5720,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125316739</v>
+        <v>125316951</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5814,10 +5760,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>589717</v>
+        <v>589777</v>
       </c>
       <c r="R47" t="n">
-        <v>6931235</v>
+        <v>6931248</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5849,7 +5795,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5859,7 +5805,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -5891,10 +5837,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125316811</v>
+        <v>132783576</v>
       </c>
       <c r="B48" t="n">
-        <v>80075</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5902,37 +5848,45 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>589717</v>
+        <v>589637</v>
       </c>
       <c r="R48" t="n">
-        <v>6931206</v>
+        <v>6931188</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5956,22 +5910,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5998,45 +5957,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125316757</v>
+        <v>125283192</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>57141</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>589713</v>
+        <v>589701</v>
       </c>
       <c r="R49" t="n">
-        <v>6931246</v>
+        <v>6931425</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6063,22 +6027,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Misstänkt natt träd ( tjäder ).</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6093,60 +6062,65 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132783581</v>
+        <v>125283936</v>
       </c>
       <c r="B50" t="n">
-        <v>80438</v>
+        <v>57141</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>589470</v>
+        <v>589597</v>
       </c>
       <c r="R50" t="n">
-        <v>6931399</v>
+        <v>6931482</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6170,22 +6144,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6212,48 +6191,53 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132783585</v>
+        <v>125284804</v>
       </c>
       <c r="B51" t="n">
-        <v>79365</v>
+        <v>57141</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>589488</v>
+        <v>589522</v>
       </c>
       <c r="R51" t="n">
-        <v>6931431</v>
+        <v>6931472</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6277,22 +6261,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6319,10 +6303,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132783577</v>
+        <v>125284424</v>
       </c>
       <c r="B52" t="n">
-        <v>80398</v>
+        <v>57132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6330,37 +6314,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>589707</v>
+        <v>589508</v>
       </c>
       <c r="R52" t="n">
-        <v>6931221</v>
+        <v>6931482</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6384,22 +6373,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6414,60 +6403,65 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132783569</v>
+        <v>125285293</v>
       </c>
       <c r="B53" t="n">
-        <v>91918</v>
+        <v>57132</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>589503</v>
+        <v>589459</v>
       </c>
       <c r="R53" t="n">
-        <v>6931444</v>
+        <v>6931441</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6491,22 +6485,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Fjäder Järpe</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6521,60 +6520,65 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>132783580</v>
+        <v>125283250</v>
       </c>
       <c r="B54" t="n">
-        <v>80438</v>
+        <v>58439</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>103018</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>589467</v>
+        <v>589679</v>
       </c>
       <c r="R54" t="n">
-        <v>6931395</v>
+        <v>6931418</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6598,22 +6602,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6640,10 +6644,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132783576</v>
+        <v>125285548</v>
       </c>
       <c r="B55" t="n">
-        <v>57958</v>
+        <v>58114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6651,45 +6655,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>589637</v>
+        <v>589543</v>
       </c>
       <c r="R55" t="n">
-        <v>6931188</v>
+        <v>6931382</v>
       </c>
       <c r="S55" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6713,27 +6714,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6760,48 +6756,52 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>132783579</v>
+        <v>125284936</v>
       </c>
       <c r="B56" t="n">
-        <v>80467</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>589469</v>
+        <v>589486</v>
       </c>
       <c r="R56" t="n">
-        <v>6931399</v>
+        <v>6931494</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6855,22 +6855,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>132783582</v>
+        <v>125285367</v>
       </c>
       <c r="B57" t="n">
-        <v>80398</v>
+        <v>106244</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6878,21 +6878,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229497</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6902,13 +6902,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>589464</v>
+        <v>589527</v>
       </c>
       <c r="R57" t="n">
-        <v>6931404</v>
+        <v>6931442</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6932,22 +6932,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6974,32 +6974,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>132783583</v>
+        <v>125283205</v>
       </c>
       <c r="B58" t="n">
-        <v>91918</v>
+        <v>97983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>589487</v>
+        <v>589702</v>
       </c>
       <c r="R58" t="n">
-        <v>6931429</v>
+        <v>6931407</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7039,22 +7039,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7081,32 +7081,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>132783586</v>
+        <v>125287027</v>
       </c>
       <c r="B59" t="n">
-        <v>80311</v>
+        <v>97983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>392</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7116,13 +7116,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>589503</v>
+        <v>589571</v>
       </c>
       <c r="R59" t="n">
-        <v>6931410</v>
+        <v>6931323</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7146,22 +7146,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7188,10 +7188,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>132783578</v>
+        <v>132783577</v>
       </c>
       <c r="B60" t="n">
-        <v>80342</v>
+        <v>80438</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7199,21 +7199,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6456</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7223,10 +7223,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>589520</v>
+        <v>589707</v>
       </c>
       <c r="R60" t="n">
-        <v>6931361</v>
+        <v>6931221</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7295,32 +7295,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132783575</v>
+        <v>132783582</v>
       </c>
       <c r="B61" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>589691</v>
+        <v>589464</v>
       </c>
       <c r="R61" t="n">
-        <v>6931244</v>
+        <v>6931404</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 11088-2025 artfynd.xlsx
+++ b/artfynd/A 11088-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783585</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783586</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284881</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125290551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783583</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283973</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285776</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284607</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283953</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1871,6 +1926,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284251</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284988</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2089,6 +2154,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783578</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2201,6 +2271,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284367</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2308,6 +2383,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2415,6 +2495,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783580</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2522,6 +2607,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783581</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2629,6 +2719,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783579</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2741,6 +2836,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285242</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2853,6 +2953,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286223</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2965,6 +3070,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286606</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125287385</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3189,6 +3304,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283801</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3306,6 +3426,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283860</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3423,6 +3548,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284312</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3540,6 +3670,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284432</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3657,6 +3792,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284981</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3774,6 +3914,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285099</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3891,6 +4036,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285335</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4008,6 +4158,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285519</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4125,6 +4280,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286059</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4242,6 +4402,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286102</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4359,6 +4524,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286321</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4476,6 +4646,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125286793</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4593,6 +4768,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125290527</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4713,6 +4893,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783576</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4830,6 +5015,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283936</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4942,6 +5132,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284804</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5054,6 +5249,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284424</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5171,6 +5371,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285293</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5283,6 +5488,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285548</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5394,6 +5604,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125284936</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5501,6 +5716,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125285367</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5608,6 +5828,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125287027</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5715,6 +5940,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783582</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5836,6 +6066,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283515</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5943,6 +6178,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283609</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6050,6 +6290,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125316757</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6157,6 +6402,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783575</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6264,6 +6514,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125316811</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6371,6 +6626,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283173</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6488,6 +6748,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283329</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6605,6 +6870,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125291148</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6722,6 +6992,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125316461</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6839,6 +7114,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125316739</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6956,6 +7236,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125316951</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7073,6 +7358,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283192</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7185,6 +7475,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283250</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7292,6 +7587,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125283205</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7399,8 +7699,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132783577</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>